--- a/校园招聘/制造业/制造业通用/技术研发类/机械工程师/2_保留题目/4轮_制造业通用_机械工程师_可保留的题目.xlsx
+++ b/校园招聘/制造业/制造业通用/技术研发类/机械工程师/2_保留题目/4轮_制造业通用_机械工程师_可保留的题目.xlsx
@@ -413,2373 +413,2188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>question_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>招聘场景</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>岗位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>技能分类</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>技能</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>知识点</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>难度</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>问题</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>第一层</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>第二层</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>第三层</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>技能分类</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>知识点</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>难度</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>行业</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>岗位</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>招聘场景</t>
+          <t>审核状态</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>一审_是否删除</t>
+          <t>参考答案-第一层</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>一审_删除原因</t>
+          <t>参考答案-第二层</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>二审_是否删除</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>二审_删除原因</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>题目是否修改</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>是否重新出题</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>一审_错误大类集合</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>二审_错误大类集合</t>
+          <t>参考答案-第三层</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>R4-Q001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>机械设计基础</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>失效模式识别</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>变形失效与刚度不足关系</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>请简单说说，当机械结构在正常载荷下出现明显弯曲或位移，这主要反映了哪方面性能不足？</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>这主要反映结构的刚度不足。刚度是指构件抵抗弹性变形的能力，在正常设计载荷作用下若产生超出工程允许范围的弯曲或位移，说明结构在该工况下的整体或局部刚度未达到设计要求，尚未涉及材料屈服或断裂，属于弹性变形超限范畴。</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>实际工作中常用三类提升刚度的方案：一是增加截面惯性矩，比如把实心轴改为空心但加厚壁厚，或把平板改用带折边、加强筋的型式，优势是不改变材料和热处理状态，制造兼容性强，但会增加重量和加工工序；二是更换高弹性模量材料，如用球墨铸铁替代灰铸铁，或选用特定牌号的调质结构钢，优势是刚度提升直接，但需重新验证铸造/切削工艺适配性及成本变化；三是优化支撑布局，比如增加中间支点或调整轴承跨距，优势是改动小、见效快，但受整机空间和装配关系约束大。综合来看，优先采用结构拓扑优化加局部加强筋的方式，既兼顾制造可行性，又避免材料升级带来的供应链和热处理工艺变更风险。</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1个异常情况概要：加工后实测刚度偏低但图纸尺寸全部合格。具体情况：焊接件经退火去应力后装配，静载测试发现悬臂端挠度超标，而所有焊缝外观、尺寸、无损检测均符合标准。解决思路：核查焊缝顺序与夹具定位是否导致残余变形累积，重点复测关键基准面在自由状态与夹紧状态下的形变差值，并安排时效振动处理后再重测。1个复杂问题概要：多部件装配后系统级刚度突降。具体问题：齿轮箱壳体单独测试刚度达标，但与电机、联轴器、底座装配成整机后，加载时输出端位移放大近三倍。解决思路：排查结合面接触刚度，实测各螺栓预紧力离散度与接触面粗糙度匹配性，优先采用分步拧紧+扭矩转角双控工艺，并在关键结合面增加0.05毫米以内厚度的刚性垫片补偿微观不平度。</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>失效模式识别</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>变形失效与刚度不足关系</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>简单</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>R4-Q002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>机械设计基础</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>材料工艺理解</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>铝合金应用边界</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>某新能源汽车电驱壳体采用压铸铝合金设计，在批量生产中发现螺栓孔周边频繁出现微裂纹，且随环境湿度升高裂纹扩展加速。已知该部位需承受装配预紧力与电机振动载荷的耦合作用，请结合铝合金的应力腐蚀开裂敏感性、压铸件内部孔隙分布特征及表面残余应力状态，说明应从哪三个关键工艺环节入手排查根本原因，并简述每个环节的验证逻辑。</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>应从压铸成型过程、机加工后处理（含去毛刺与倒角）、以及表面防护工艺这三个环节入手排查。因为压铸环节决定内部孔隙与热节残留应力分布；机加工环节会改变原压铸表层应力场并可能引入新应力集中；表面防护则直接影响铝合金在湿热环境下的电化学稳定性，三者共同构成应力腐蚀开裂发生的必要条件。</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>第一是压铸参数控制：重点验证模具温度、慢压射速度和保压时间是否导致局部冷却不均或缩松聚集，可通过同批次解剖件做X光断层扫描比对孔隙率分布；第二是机加工工艺：核查钻孔与攻丝是否采用无冷却液干切或低进给量，避免表层晶粒撕裂与拉应力叠加，验证方式是在裂纹高发区做盲孔法残余应力测试；第三是表面处理：确认钝化膜是否完整覆盖螺纹根部，尤其关注阳极氧化封孔质量，验证手段为盐雾试验后做断口形貌能谱分析。其中机加工环节验证时效性最高、成本最低、干预最直接，应优先排查。</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>1个异常情况概要：螺栓孔底角处出现沿晶微裂纹，具体情况是攻丝后未做倒圆处理，导致几何突变与残余拉应力叠加，在湿热环境下诱发应力腐蚀；解决思路是将机加工工序卡控点前移，强制要求M6及以上螺纹必须执行R0.2以上刀具倒角，并在首件检验中增加放大镜目视检查。1个复杂问题概要：同一压铸批次不同模腔生产的壳体裂纹发生率差异超3倍，具体问题是多腔模具各型腔冷却速率不一致，造成残余应力梯度离散；解决思路是联合模具厂开展模温均衡性标定，用红外热像仪实测合模状态下各型腔表面温度波动，将温差控制在±5℃以内，并同步更新工艺作业指导书中的模温监控频次。</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>材料工艺理解</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>铝合金应用边界</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>R4-Q004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>工程图与公差</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>工程图表达</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>主视图与剖视图选择逻辑</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>在绘制一个带中心通孔、两侧对称凸缘及底部安装面的法兰盘零件图时，主视图采用沿轴线剖切的全剖视图。请简述为什么这个剖切位置能最有效地表达内部结构和关键尺寸关系。</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>因为法兰盘是典型的回转对称类零件，其核心功能结构——中心通孔、凸缘厚度与位置、安装面到孔轴线的距离——都分布在轴向截面上；沿轴线剖切的全剖视图能一次性完整暴露所有这些位于同一纵向对称平面内的内部形体和关联尺寸，避免多视图拼凑理解，符合主视图应优先呈现零件主要形状特征和装配关系的基本制图原则。</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>工程上常用三种剖切方案：一是轴线全剖，二是偏心局部剖，三是旋转剖。轴线全剖优势在于直接展示通孔直径、凸缘内外径差、凸缘厚度、底面到孔端面距离等全部关键尺寸链，且与后续数控车削或车铣复合加工基准天然一致；偏心局部剖虽保留部分外形，但会割裂凸缘对称性表达，增加读图误差；旋转剖则适用于阶梯轴类，对法兰盘这类端面承载为主的结构反而弱化底面安装关系。综合制造准备效率、检测可实施性与设计意图传达准确性，轴线全剖是当前制造业一线最主流且被标准图纸库验证过的首选方案。</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>1个异常情况概要：剖切后凸缘轮廓被误标为实线而非双点划线。具体情况：绘图员将未被剖切到的远侧凸缘外缘按可见轮廓线绘制，导致工艺人员误判为实体结构，引发车削余量预留错误。解决思路：严格依据GB/T 4458.6标准中‘不可见轮廓不画’原则，确认该轮廓属于剖切平面后方、且未被剖到的部分，应省略或按假想投影处理。1个复杂问题概要：底部安装面与中心孔轴线的垂直度公差在剖视图中难以直接标注。具体问题：全剖后安装面投影为一条直线，无法体现面要素，导致形位公差框格无基准可依。解决思路：在俯视图或单独的局部放大图中补充安装面投影，并以中心孔轴线为基准引出垂直度要求，确保检测时可用三坐标或平台打表法实测。</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>工程图表达</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>主视图与剖视图选择逻辑</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>R4-Q005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>工程图与公差</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>工程图表达</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>装配图与零件图表达差异</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>某减速箱装配图中，轴承座与端盖通过四颗螺栓紧固，并在装配图上用局部视图加引出线标注了‘螺栓预紧力矩：25N·m’；而这两类零件的单独图纸上均未出现力矩要求。为什么这个预紧力矩参数必须出现在装配图中，而不是由螺栓规格或材料强度自行推导确定？请简述原因。</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>因为预紧力矩是装配层级的工艺控制参数，它取决于轴承座与端盖之间的接合面状态、垫片有无、润滑条件、装配顺序及整机功能需求，这些信息只存在于装配关系中，零件图无法承载；装配图作为指导现场拧紧作业的唯一法定依据，必须明确标出该参数，否则无法保证轴承预紧刚度和轴向定位精度。</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>常见方案有三种：一是按螺栓等级查表取推荐力矩，但未考虑实际接触面摩擦系数变化，易导致过紧或松动；二是依据零件图标注的螺纹规格和材料牌号反算理论值，但忽略了端盖刚度变形对预紧力再分配的影响；三是直接引用整机试验验证后的装配力矩值，该方案最可靠，因为它覆盖了真实工况下的界面配合、热变形协调和载荷传递路径。当前行业普遍采用第三种，即基于台架试验+过程能力验证后固化到装配图，兼顾可复现性与制造节拍要求。</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1个异常情况概要：装配现场使用非原厂润滑脂导致实测力矩达标但预紧力不足。具体情况：操作员误用含二硫化钼的防卡剂替代装配专用油，界面摩擦系数降低约30%，相同力矩下螺栓轴向拉力超差，引发端盖微变形和轴承游隙失准。解决思路：在装配图技术要求栏同步注明‘仅允许使用XX型号装配润滑油’，并纳入首件拧紧力矩-伸长量双参数确认项。1个复杂问题概要：多螺栓对称紧固时因端盖局部刚度不均造成预紧力离散。具体问题：铸铁端盖厚薄过渡区存在残余应力，四颗螺栓按交叉顺序拧紧后，实测预紧力偏差达±18%。解决思路：在装配图中增加‘分两轮拧紧：首轮50%力矩，第二轮100%力矩并按顺时针逐颗复核’的工艺注释，并配套提供扭矩扳手校验记录表模板。</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>工程图表达</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>装配图与零件图表达差异</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>R4-Q006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>工程图与公差</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>工程图表达</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>装配图与零件图表达差异</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>在装配图中，两个配合的轴和孔零件分别标注了Φ40H7/g6，但各自零件图上只标出直径尺寸和公差带代号，未标配合性质。为什么装配图必须明确用‘Φ40H7/g6’形式表达这对配合，而不能仅靠两个零件图上的独立公差信息来确保现场装配时能正确识别间隙配合关系？请简述原因。</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>因为装配图的核心功能是表达零部件之间的装配关系和配合要求，而配合性质——比如是间隙、过渡还是过盈——不能仅从单个零件的公差带代号反向推断出来。H7和g6这两个代号本身只说明孔和轴各自相对于基本尺寸的公差范围和位置，但只有把它们组合起来看，才能确定这是标准间隙配合。单独看零件图，工人或检验员无法直接判断这对尺寸在装配后是否留有间隙、间隙大小是否满足功能要求。</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>实际工作中有三种常见处理方式：第一种是仅在零件图上标公差带代号，依赖工艺人员查表换算，但易出错且耗时，尤其对新员工或跨班组协作时风险高；第二种是在装配图上用Φ40H7/g6完整标注，配合技术条件文字说明，这是当前主流做法，信息直达、无歧义、适配数控编程和三坐标检测路径设置；第三种是在BOM表或工艺卡片中补充配合说明，但存在图纸与文档脱节风险，一旦版本不一致就导致错装。综合来看，装配图直接标注Φ40H7/g6是最可靠的方式，它把配合意图固化在设计源头，兼顾识图效率、制造一致性与质量追溯性。</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1个异常情况概要：现场误将g6轴当作h6或f7使用。具体情况：某批次轴零件图误印为g6，实为f7，但装配图仍写Φ40H7/g6，操作工按图领料装配后出现间隙过大、定位松动。解决思路：装配图必须与零件图公差代号严格联动校核，推行设计-工艺联合审签机制，关键配合项需在PLM系统中设置自动比对预警。1个复杂问题概要：同一轴需与多个孔配合，但配合性质不同。具体问题：一根传动轴先后与轴承座孔（H7/g6）、联轴器孔（H7/k6）配合，若装配图未分段标注，易造成混装或热装工艺误用。解决思路：在装配图对应部位用指引线分段标注配合代号，并在技术要求中注明‘同一轴不同配合段不得互换’，同步更新工序卡中的装配顺序与检测点。</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>工程图表达</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>装配图与零件图表达差异</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>在装配尺寸链中，由多个零件尺寸累积形成的最终间隙，这个间隙尺寸被称为什么环？</t>
+          <t>R4-Q008</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>这个间隙尺寸被称为封闭环。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>在机械工程师日常的装配公差分析工作中，封闭环的识别和控制有三种主流做法：一是基于二维工程图的手动尺寸链追踪，优点是直观、无需软件、符合图纸审查习惯，但易漏掉隐藏装配关系，尤其在多自由度叠压结构中；二是用三维CAD装配体自动提取尺寸链，能覆盖空间叠加路径，但依赖模型几何完整性与约束定义质量，对未完全约束或柔性件建模不敏感；三是借助专用公差分析软件（如Creo TolAnalyst、Siemens Dimensional Engineering）进行闭环仿真，可量化各组成环贡献率，但需提前完成公差分配与工艺能力输入，耗时略长。综合来看，在量产前设计评审阶段，优先采用CAD装配体辅助追踪+人工校核的方式，既保障时效性，又兼顾对装配顺序、基准传递、装夹变形等实际工况的判断能力。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1个异常情况概要：封闭环实测超差但所有组成环均在图纸公差内。具体情况：某变速箱壳体与端盖装配后轴向间隙超差0.08mm，但所有单件尺寸检测合格，根源是端盖螺栓孔位置度偏差与壳体对应孔位形成累积偏载，导致端盖微倾斜，间隙非均匀分布。解决思路：回归装配基准体系，检查定位销与螺栓孔的功能分工，将位置度公差从孔组整体管控改为以定位孔为基准、其余孔按最大实体要求标注。1个复杂问题概要：多零件串联装配中封闭环受热变形影响显著。具体问题：高温工况下涡轮增压器中间体与轴承座装配间隙发生非线性收缩，导致冷态合格、热态卡滞。解决思路：在尺寸链中引入材料线膨胀系数与典型工况温升作为修正因子，将常温封闭环设定为补偿值，并通过装配预留过盈量或设置弹性补偿结构来平衡热变形效应。</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>尺寸链分析</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>装配间隙尺寸链判断</t>
+          <t>形位公差应用</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>同轴度与圆跳动差异</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某精密减速器输出轴与壳体轴承孔需保证长期运转下的同心稳定，设计图中在轴承孔上标注了以输出轴轴线为基准的同轴度公差，而实际检测时发现：各截面圆跳动均合格，但整轴旋转时轴承温升异常且寿命显著缩短。请简述该现象反映出的几何误差本质差异，并说明为何仅控制圆跳动不足以保障此工况下的配合稳定性。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>圆跳动控制的是单个横截面轮廓相对于基准轴线的径向偏移，反映的是局部、瞬时的旋转偏差；同轴度控制的是整个被测轴线（即轴承孔中心线）相对于基准轴线（输出轴理论轴线）的整体空间位置一致性。两者约束对象不同：圆跳动管‘点’或‘段’的跳变，同轴度管‘线’的走向和位置。</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>工程中常见三种方案：一是按图纸严格执行同轴度检测，用三坐标测量机沿孔全长采集多截面中心点拟合轴线，精度高但耗时长；二是改标圆柱度+位置度组合，兼顾形状与定位，检测效率提升但需重新验证装配刚度影响；三是采用功能检具模拟装配状态检测，如带基准轴芯棒+千分表扫掠，时效性好且贴近实际工况，但检具需随批次校准。综合来看，功能检具法最适配批量生产场景，在保证检测时效前提下，能暴露轴线弯曲、倾斜等同轴度失效模式，是当前产线主流选择。</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>1个异常情况概要：检测合格但运行失效。具体情况：圆跳动合格仅说明各截面圆心未大幅偏移，但轴承孔轴线可能存在整体倾斜或弯曲，导致轴承内外圈在旋转中产生交变偏载，引发滚子边缘接触、润滑膜破裂。解决思路：回归装配体级验证，用激光跟踪仪或高精度芯棒+电子水平仪复测孔轴线全段方向偏差，并结合轴承预紧力实测数据反推同轴度容差边界。1个复杂问题概要：同轴度公差与轴承游隙、壳体刚度耦合失配。具体问题：铸铁壳体在螺栓预紧和热变形下发生微变形，使原本合格的同轴度在装机后劣化。解决思路：在工艺文件中明确壳体精镗工序必须在模拟装配压紧状态下进行，并将轴承座周边支撑刚度纳入GD&amp;T标注的基准体系，而非仅依赖自由状态检测结果。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>请简单说说，判断焊接可达性时，为什么需要同时考虑焊枪的伸入空间和转动角度？</t>
+          <t>R4-Q009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>因为机械工程师在结构设计和工艺协同阶段，必须确保焊枪既能物理进入待焊位置，又能在该位置完成稳定摆动和送丝动作；仅满足伸入空间但无法调整姿态，会导致熔池成形不良、未熔合或飞溅失控；仅满足转动角度但入口被遮挡，则根本无法就位。二者缺一不可，共同构成焊枪实际作业的运动包络边界。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>目前常用方案有三类：一是基于三维模型的焊枪数字包络体仿真，优势是前期介入早、可批量验证，但依赖模型精度和焊枪库完整性；二是实物焊枪+关节臂测量的现场工装模拟，优势是真实反映干涉和操作手感，但耗时长、成本高，不适合早期方案比选；三是结合典型焊缝节拍要求的简化姿态角阈值法，比如规定最小±30度俯仰+±45度偏转，优势是评审效率高，但易漏判狭长腔体内的复合姿态受限。综合来看，数字包络体仿真最适合机械工程师在设计输出前主导开展，兼顾时效性与覆盖度，且能与下游工艺文件直接衔接。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>异常情况概要：焊缝位置被邻近加强筋或管路支架意外遮挡。具体情况：结构图纸未标注装配顺序，导致先焊主梁后装支架，而支架恰好卡死焊枪侧向转动空间。解决思路：在三维装配干涉检查中增加‘焊枪就位路径+姿态’双维度验证，并将关键焊缝附近的可拆卸件设为工艺预留项。复杂问题概要：多层薄壁筒体环焊缝内侧可达性不足。具体问题：外壁已安装法兰和传感器支架，焊枪从端口伸入后因筒体直径小、长度大，末端无法获得足够转动角度完成全周均匀焊接。解决思路：优先采用内孔式自动焊设备替代手持焊枪；若必须人工焊，则需在结构设计阶段预留工艺窗口，或协调将该焊缝调整为外侧坡口+反变形控制的单面焊双面成形方案。</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>制造工艺</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>焊接工艺</t>
+          <t>工程图与公差</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>焊接可达性判断</t>
+          <t>尺寸链分析</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>装配间隙尺寸链判断</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>简单</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>在装配尺寸链中，由多个零件尺寸累积形成的最终间隙，这个间隙尺寸被称为什么环？</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>这个间隙尺寸被称为封闭环。</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>在机械工程师日常的装配公差分析工作中，封闭环的识别和控制有三种主流做法：一是基于二维工程图的手动尺寸链追踪，优点是直观、无需软件、符合图纸审查习惯，但易漏掉隐藏装配关系，尤其在多自由度叠压结构中；二是用三维CAD装配体自动提取尺寸链，能覆盖空间叠加路径，但依赖模型几何完整性与约束定义质量，对未完全约束或柔性件建模不敏感；三是借助专用公差分析软件（如Creo TolAnalyst、Siemens Dimensional Engineering）进行闭环仿真，可量化各组成环贡献率，但需提前完成公差分配与工艺能力输入，耗时略长。综合来看，在量产前设计评审阶段，优先采用CAD装配体辅助追踪+人工校核的方式，既保障时效性，又兼顾对装配顺序、基准传递、装夹变形等实际工况的判断能力。</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>1个异常情况概要：封闭环实测超差但所有组成环均在图纸公差内。具体情况：某变速箱壳体与端盖装配后轴向间隙超差0.08mm，但所有单件尺寸检测合格，根源是端盖螺栓孔位置度偏差与壳体对应孔位形成累积偏载，导致端盖微倾斜，间隙非均匀分布。解决思路：回归装配基准体系，检查定位销与螺栓孔的功能分工，将位置度公差从孔组整体管控改为以定位孔为基准、其余孔按最大实体要求标注。1个复杂问题概要：多零件串联装配中封闭环受热变形影响显著。具体问题：高温工况下涡轮增压器中间体与轴承座装配间隙发生非线性收缩，导致冷态合格、热态卡滞。解决思路：在尺寸链中引入材料线膨胀系数与典型工况温升作为修正因子，将常温封闭环设定为补偿值，并通过装配预留过盈量或设置弹性补偿结构来平衡热变形效应。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>某重型工程机械的传动轴在批量服役中出现早期疲劳断裂，材质为42CrMoA调质钢，原工艺为850℃淬火+600℃高温回火。检测发现断口附近存在未完全回火的孪晶马氏体组织。请简述你如何综合考虑服役载荷特征、组织稳定性要求与后续机加工余量约束，重新评估并调整该零件的热处理路径。</t>
+          <t>R4-Q010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>42CrMoA是国标GB/T 3077规定的中碳合金结构钢，调质处理需兼顾强度、韧性和组织均匀性；孪晶马氏体是淬火后未充分回火残留的高硬度、低韧性组织，会显著降低疲劳抗力；原工艺中600℃回火虽在常规范围，但若保温时间不足、炉温均匀性差或装炉量过大，易导致心部或截面突变处回火不充分。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>方案一：延长600℃回火保温时间并增加炉温均匀性验证——提升组织转化充分性，但可能加剧尺寸变形，影响后续精加工余量控制；方案二：改用620℃回火——提高回火稳定性，促进残余奥氏体分解和碳化物球化，但需复核屈服强度是否满足轴类扭转-弯曲复合载荷要求；方案三：采用两段回火（600℃+620℃），先消除应力再稳定组织——兼顾变形控制与组织均匀性，但增加工序和能耗；综合权衡下，优先选用方案二，并同步校核机加工余量实测变形数据，因重型传动轴对疲劳寿命敏感度高于静态强度冗余度。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1个异常情况概要：回火后实测硬度局部偏高。具体情况：同一炉零件不同位置硬度差超HRC2，对应断口区域显微组织仍见孪晶马氏体残迹。解决思路：排查炉内温度分区偏差及零件摆放密度，引入随炉热电偶测温验证，而非仅依赖仪表控温。1个复杂问题概要：热处理变形超精加工余量。具体问题：轴颈部位径向变形量达0.12mm，超出图纸标注的0.08mm机加工余量上限。解决思路：在保证回火充分前提下，优化淬火冷却方式（如改用PAG水溶性介质控冷），并结合校直工序与终检余量实测闭环，将变形纳入热处理工艺放行条件。</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>材料工艺理解</t>
+          <t>制造工艺</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>热处理方法选择</t>
+          <t>焊接工艺</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>焊接可达性判断</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>请简单说说，判断焊接可达性时，为什么需要同时考虑焊枪的伸入空间和转动角度？</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>因为机械工程师在结构设计和工艺协同阶段，必须确保焊枪既能物理进入待焊位置，又能在该位置完成稳定摆动和送丝动作；仅满足伸入空间但无法调整姿态，会导致熔池成形不良、未熔合或飞溅失控；仅满足转动角度但入口被遮挡，则根本无法就位。二者缺一不可，共同构成焊枪实际作业的运动包络边界。</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>目前常用方案有三类：一是基于三维模型的焊枪数字包络体仿真，优势是前期介入早、可批量验证，但依赖模型精度和焊枪库完整性；二是实物焊枪+关节臂测量的现场工装模拟，优势是真实反映干涉和操作手感，但耗时长、成本高，不适合早期方案比选；三是结合典型焊缝节拍要求的简化姿态角阈值法，比如规定最小±30度俯仰+±45度偏转，优势是评审效率高，但易漏判狭长腔体内的复合姿态受限。综合来看，数字包络体仿真最适合机械工程师在设计输出前主导开展，兼顾时效性与覆盖度，且能与下游工艺文件直接衔接。</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>异常情况概要：焊缝位置被邻近加强筋或管路支架意外遮挡。具体情况：结构图纸未标注装配顺序，导致先焊主梁后装支架，而支架恰好卡死焊枪侧向转动空间。解决思路：在三维装配干涉检查中增加‘焊枪就位路径+姿态’双维度验证，并将关键焊缝附近的可拆卸件设为工艺预留项。复杂问题概要：多层薄壁筒体环焊缝内侧可达性不足。具体问题：外壁已安装法兰和传感器支架，焊枪从端口伸入后因筒体直径小、长度大，末端无法获得足够转动角度完成全周均匀焊接。解决思路：优先采用内孔式自动焊设备替代手持焊枪；若必须人工焊，则需在结构设计阶段预留工艺窗口，或协调将该焊缝调整为外侧坡口+反变形控制的单面焊双面成形方案。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>位置度公差标注在孔位上时，它主要约束的是该孔的实际中心点相对于理想位置的什么偏差？</t>
+          <t>R4-Q012</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>它约束的是该孔实际中心点相对于理论正确位置在二维平面内（即垂直于基准轴线的投影面上）的综合位置偏差，也就是实际中心点偏离理想位置的最大允许偏移量。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>在机械工程师日常工作中，实现位置度控制主要有四种常用方案：一是采用高精度钻模或组合夹具定位加工，优势是重复性好、适合中小批量，但柔性差、换型成本高；二是使用三坐标测量机引导数控铣床进行在线补偿加工，优势是适应多品种小批量、能闭环修正，但依赖操作人员对基准转换的理解深度；三是基于基准优先级设计专用检具进行通止规检测，优势是现场快速判定、产线节拍匹配度高，但仅能判断合格与否，无法反馈偏差方向；四是通过激光跟踪仪配合数模比对进行大尺寸结构件孔位验证，优势是覆盖范围广、无累积误差，但设备成本高、环境要求严。综合来看，中小批量机加件首选数控加工+三坐标抽检闭环方案，它兼顾工艺可控性、检测可追溯性和产线适配性。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>异常情况概要：基准体系理解错误导致位置度检测结果失真。具体情况：工程师将辅助基准误作第一基准，或未按图纸标注顺序建立基准系，造成实际测量坐标系与设计意图不一致，使合格零件被判超差。解决思路：严格依据图纸基准字母顺序和符号类型（如A-B-C），在检测前用模拟块或基准销实物复现基准要素，确认基准约束状态后再采集数据。复杂问题概要：薄壁结构件在装配压紧状态下孔位位置度合格，但松开后回弹超差。具体问题：因工件刚度不足，检测时外力引起的弹性变形掩盖了真实位置偏差，导致交付后装配干涉。解决思路：在检测时模拟真实装配压紧状态施加等效力，并结合有限元预判回弹趋势，在加工余量中预留反向补偿量，同时对关键孔位增加时效处理工序以稳定残余应力。</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>形位公差应用</t>
+          <t>机械设计基础</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>位置度对装配功能的约束</t>
+          <t>材料工艺理解</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>热处理方法选择</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某重型工程机械的传动轴在批量服役中出现早期疲劳断裂，材质为42CrMoA调质钢，原工艺为850℃淬火+600℃高温回火。检测发现断口附近存在未完全回火的孪晶马氏体组织。请简述你如何综合考虑服役载荷特征、组织稳定性要求与后续机加工余量约束，重新评估并调整该零件的热处理路径。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>42CrMoA是国标GB/T 3077规定的中碳合金结构钢，调质处理需兼顾强度、韧性和组织均匀性；孪晶马氏体是淬火后未充分回火残留的高硬度、低韧性组织，会显著降低疲劳抗力；原工艺中600℃回火虽在常规范围，但若保温时间不足、炉温均匀性差或装炉量过大，易导致心部或截面突变处回火不充分。</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>方案一：延长600℃回火保温时间并增加炉温均匀性验证——提升组织转化充分性，但可能加剧尺寸变形，影响后续精加工余量控制；方案二：改用620℃回火——提高回火稳定性，促进残余奥氏体分解和碳化物球化，但需复核屈服强度是否满足轴类扭转-弯曲复合载荷要求；方案三：采用两段回火（600℃+620℃），先消除应力再稳定组织——兼顾变形控制与组织均匀性，但增加工序和能耗；综合权衡下，优先选用方案二，并同步校核机加工余量实测变形数据，因重型传动轴对疲劳寿命敏感度高于静态强度冗余度。</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>1个异常情况概要：回火后实测硬度局部偏高。具体情况：同一炉零件不同位置硬度差超HRC2，对应断口区域显微组织仍见孪晶马氏体残迹。解决思路：排查炉内温度分区偏差及零件摆放密度，引入随炉热电偶测温验证，而非仅依赖仪表控温。1个复杂问题概要：热处理变形超精加工余量。具体问题：轴颈部位径向变形量达0.12mm，超出图纸标注的0.08mm机加工余量上限。解决思路：在保证回火充分前提下，优化淬火冷却方式（如改用PAG水溶性介质控冷），并结合校直工序与终检余量实测闭环，将变形纳入热处理工艺放行条件。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>在汽车发动机缸盖螺栓装配过程中，常采用扭矩-转角法拧紧。请简述这种方法如何通过控制螺栓的轴向预紧力来提升防松可靠性。</t>
+          <t>R4-Q013</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>扭矩-转角法是先施加较小的初始扭矩，使螺栓贴合被连接件并消除间隙；再以该点为起点，继续按设定角度旋转螺栓。该方法实质是利用螺栓自身的伸长量（由转角换算）来间接、稳定地控制其轴向预紧力，避免单纯依赖扭矩时因摩擦系数波动导致预紧力离散过大，从而保障缸盖密封和螺栓服役期间的夹紧力稳定性，提升防松可靠性。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>当前主流方案有三种：一是纯扭矩控制法，操作简单但受润滑状态、表面粗糙度影响大，预紧力波动常超±30%，已基本不用于缸盖关键螺栓；二是屈服点控制法，精度高但需实时监测扭矩-转角曲线拐点，对传感器和控制系统要求严，多用于高端研发产线，量产普及率低；三是扭矩-转角法，兼顾精度、成本与产线适应性——它绕开了摩擦系数不可控的问题，用刚性段的螺纹导程关系将转角转化为可靠伸长，预紧力离散可控制在±8%以内，且适配现有拧紧机和SPC监控体系，是当前主流量产线首选。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1个异常情况概要：拧紧过程中出现转角达标但终拧扭矩偏低。具体情况：常见于螺纹润滑过度或螺栓牙型轻微损伤，导致螺纹副刚度下降，相同伸长量下所需扭矩减小，易误判为合格，实则预紧力不足。解决思路：在工艺文件中设定扭矩下限阈值，并与转角联合判定；同时在首件和每班次抽检中增加松脱扭矩复测，验证夹紧力保持能力。1个复杂问题概要：缸盖多螺栓协同拧紧时，后序螺栓拧紧引发已拧紧螺栓预紧力衰减。具体问题：因缸盖刚度分布不均及热变形叠加，第5颗螺栓拧紧可能使第1颗预紧力下降5%～10%。解决思路：采用分步、交叉、递增的拧紧顺序策略，并在终拧后4小时内安排静态扭矩抽检，结合缸盖变形仿真结果优化拧紧路径，而非仅依赖单颗螺栓控制参数。</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>连接与紧固设计</t>
+          <t>工程图与公差</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>螺栓连接防松原理</t>
+          <t>形位公差应用</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>位置度对装配功能的约束</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>位置度公差标注在孔位上时，它主要约束的是该孔的实际中心点相对于理想位置的什么偏差？</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>它约束的是该孔实际中心点相对于理论正确位置在二维平面内（即垂直于基准轴线的投影面上）的综合位置偏差，也就是实际中心点偏离理想位置的最大允许偏移量。</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>在机械工程师日常工作中，实现位置度控制主要有四种常用方案：一是采用高精度钻模或组合夹具定位加工，优势是重复性好、适合中小批量，但柔性差、换型成本高；二是使用三坐标测量机引导数控铣床进行在线补偿加工，优势是适应多品种小批量、能闭环修正，但依赖操作人员对基准转换的理解深度；三是基于基准优先级设计专用检具进行通止规检测，优势是现场快速判定、产线节拍匹配度高，但仅能判断合格与否，无法反馈偏差方向；四是通过激光跟踪仪配合数模比对进行大尺寸结构件孔位验证，优势是覆盖范围广、无累积误差，但设备成本高、环境要求严。综合来看，中小批量机加件首选数控加工+三坐标抽检闭环方案，它兼顾工艺可控性、检测可追溯性和产线适配性。</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>异常情况概要：基准体系理解错误导致位置度检测结果失真。具体情况：工程师将辅助基准误作第一基准，或未按图纸标注顺序建立基准系，造成实际测量坐标系与设计意图不一致，使合格零件被判超差。解决思路：严格依据图纸基准字母顺序和符号类型（如A-B-C），在检测前用模拟块或基准销实物复现基准要素，确认基准约束状态后再采集数据。复杂问题概要：薄壁结构件在装配压紧状态下孔位位置度合格，但松开后回弹超差。具体问题：因工件刚度不足，检测时外力引起的弹性变形掩盖了真实位置偏差，导致交付后装配干涉。解决思路：在检测时模拟真实装配压紧状态施加等效力，并结合有限元预判回弹趋势，在加工余量中预留反向补偿量，同时对关键孔位增加时效处理工序以稳定残余应力。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>某自动化产线的精密定位平台在长期运行后出现重复定位偏差增大，检测发现导轨支承刚度下降但材料未屈服。请简述你如何区分刚度失效与强度失效的工程表征，并说明在寿命中期维护中，应依据哪些实测参数来重新校核刚度与强度的设计边界。</t>
+          <t>R4-Q014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>刚度失效的工程表征是结构在工作载荷下产生超出允许范围的弹性变形，表现为重复定位偏差增大、回程误差变大、动态响应滞后，但材料表面无塑性痕迹、残余变形可恢复、硬度与金相组织无异常；强度失效的工程表征是材料局部发生不可逆的塑性变形或断裂，典型现象包括支承面压溃凹痕、导轨边缘微裂纹、螺栓头根部颈缩、或出现肉眼可见的永久位移，且常伴随硬度梯度异常或微观组织屈服带。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>在寿命中期维护中，需同步采集三类实测参数：一是刚度边界校核参数，包括导轨支承面接触压痕深度（用便携式轮廓仪测）、预紧螺栓实际扭矩衰减率（对比原始装配记录）、滑块在额定负载下的位移-力迟滞曲线斜率变化；二是强度边界校核参数，包括支承座关键截面实测应力集中系数（通过贴片式应变计阵列获取）、导轨安装面边缘的微裂纹萌生状态（工业内窥镜+荧光渗透复查）、以及热处理区域硬度梯度分布（便携式里氏硬度仪沿轴向每50mm测三点）；三是关联性参数，如润滑脂成分衰变程度（红外光谱快检）和基座地脚螺栓预紧力离散度——这三类参数缺一不可，其中接触压痕深度和应力集中系数最具判别力，因前者直接反映界面刚度退化主因，后者能最早暴露局部强度裕度耗尽风险。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1个异常情况概要：导轨支承刚度下降但硬度检测合格。具体情况：便携硬度仪读数在标准范围内，但压痕深度超限，说明表面硬化层完好，但底层基体因微动磨损或残余应力松弛导致支撑刚度劣化。解决思路：不依赖硬度单指标，必须结合接触刚度测试（如静刚度加载-位移法）和支承座底面贴合率检测（蓝油法+数字图像比对），确认是否为界面间隙扩大所致。1个复杂问题概要：预紧螺栓扭矩衰减与支承刚度下降非线性耦合。具体问题：多个M12螺栓预紧力离散度达35%，导致局部支承刚度骤降，但整体平均扭矩仍满足下限，常规抽检易漏判。解决思路：采用螺栓群全数扭矩-转角双参数扫描，结合支承座底面应变云图反演载荷分布，识别低刚度区并针对性重紧+补充垫片，而非统一复拧。</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>机械设计基础</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>机构与载荷分析</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>刚度与强度设计边界</t>
+          <t>连接与紧固设计</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>螺栓连接防松原理</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>在汽车发动机缸盖螺栓装配过程中，常采用扭矩-转角法拧紧。请简述这种方法如何通过控制螺栓的轴向预紧力来提升防松可靠性。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>扭矩-转角法是先施加较小的初始扭矩，使螺栓贴合被连接件并消除间隙；再以该点为起点，继续按设定角度旋转螺栓。该方法实质是利用螺栓自身的伸长量（由转角换算）来间接、稳定地控制其轴向预紧力，避免单纯依赖扭矩时因摩擦系数波动导致预紧力离散过大，从而保障缸盖密封和螺栓服役期间的夹紧力稳定性，提升防松可靠性。</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>当前主流方案有三种：一是纯扭矩控制法，操作简单但受润滑状态、表面粗糙度影响大，预紧力波动常超±30%，已基本不用于缸盖关键螺栓；二是屈服点控制法，精度高但需实时监测扭矩-转角曲线拐点，对传感器和控制系统要求严，多用于高端研发产线，量产普及率低；三是扭矩-转角法，兼顾精度、成本与产线适应性——它绕开了摩擦系数不可控的问题，用刚性段的螺纹导程关系将转角转化为可靠伸长，预紧力离散可控制在±8%以内，且适配现有拧紧机和SPC监控体系，是当前主流量产线首选。</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>1个异常情况概要：拧紧过程中出现转角达标但终拧扭矩偏低。具体情况：常见于螺纹润滑过度或螺栓牙型轻微损伤，导致螺纹副刚度下降，相同伸长量下所需扭矩减小，易误判为合格，实则预紧力不足。解决思路：在工艺文件中设定扭矩下限阈值，并与转角联合判定；同时在首件和每班次抽检中增加松脱扭矩复测，验证夹紧力保持能力。1个复杂问题概要：缸盖多螺栓协同拧紧时，后序螺栓拧紧引发已拧紧螺栓预紧力衰减。具体问题：因缸盖刚度分布不均及热变形叠加，第5颗螺栓拧紧可能使第1颗预紧力下降5%～10%。解决思路：采用分步、交叉、递增的拧紧顺序策略，并在终拧后4小时内安排静态扭矩抽检，结合缸盖变形仿真结果优化拧紧路径，而非仅依赖单颗螺栓控制参数。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>某精密齿轮箱的输出轴端跳动超差，该跳动由箱体轴承孔位置度、轴承外圈配合面圆柱度、轴承内圈与轴配合面同轴度、以及轴肩端面垂直度四个要素共同影响。请简述你如何运用极值法公差叠加逻辑，识别其中对封闭环跳动贡献最大的尺寸环，并说明在不增加检测成本的前提下，应优先收紧哪个环的公差及其工程依据。</t>
+          <t>R4-Q016</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>极值法公差叠加是把各组成环公差按最不利方向线性相加，得到封闭环最大可能偏差的方法。它不考虑概率分布，只关注设计允许的极限组合。题干中封闭环是输出轴端跳动，四个组成环分别是箱体轴承孔位置度、轴承外圈配合面圆柱度、轴承内圈与轴配合面同轴度、轴肩端面垂直度——这四个环的偏差方向若全部朝同一侧叠加，就会导致端跳动达到理论最大值。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>实际工作中常用三种分析方式：一是基于装配顺序做矢量分解，把每个环在跳动敏感方向的投影量化；二是用实物测量数据反推各环贡献占比，比如分别单件复测再组装验证；三是借助公差分析软件做极值敏感度排序。第一种最依赖经验但无需额外设备；第二种最可靠但耗时长；第三种效率高但需建模基础。综合来看，在不增加检测成本前提下，首选第一种——通过结构刚度和装配约束判断各环在径向跳动方向的实际传递效率，例如轴承外圈配合面圆柱度直接影响外圈变形后对内圈的偏斜传递，而轴肩端面垂直度主要影响轴向定位，对径向跳动的耦合效应较弱。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1个异常情况概要：轴承外圈配合面圆柱度实测合格但装入箱体后跳动仍超差。具体情况：箱体轴承孔刚性不足，压装时局部挤压导致外圈椭圆化，原圆柱度检测未模拟装配应力状态。解决思路：改用带预紧力的模拟工装检测，或在工艺文件中明确压装力与保压时间控制要求。1个复杂问题概要：四个组成环公差均在图纸范围内，但整机跳动仍不稳定。具体问题：轴承内圈与轴配合面同轴度受热装工艺波动影响大，冷态合格、热态装配后因温差收缩不均引发微偏心。解决思路：将该环公差收紧一级，并在作业指导书中固化加热温度、轴向压入速度和冷却静置时长三个关键参数。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>工程图与公差</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>尺寸链分析</t>
+          <t>机械设计基础</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>极值法公差叠加逻辑</t>
+          <t>机构与载荷分析</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>刚度与强度设计边界</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某自动化产线的精密定位平台在长期运行后出现重复定位偏差增大，检测发现导轨支承刚度下降但材料未屈服。请简述你如何区分刚度失效与强度失效的工程表征，并说明在寿命中期维护中，应依据哪些实测参数来重新校核刚度与强度的设计边界。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>刚度失效的工程表征是结构在工作载荷下产生超出允许范围的弹性变形，表现为重复定位偏差增大、回程误差变大、动态响应滞后，但材料表面无塑性痕迹、残余变形可恢复、硬度与金相组织无异常；强度失效的工程表征是材料局部发生不可逆的塑性变形或断裂，典型现象包括支承面压溃凹痕、导轨边缘微裂纹、螺栓头根部颈缩、或出现肉眼可见的永久位移，且常伴随硬度梯度异常或微观组织屈服带。</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>在寿命中期维护中，需同步采集三类实测参数：一是刚度边界校核参数，包括导轨支承面接触压痕深度（用便携式轮廓仪测）、预紧螺栓实际扭矩衰减率（对比原始装配记录）、滑块在额定负载下的位移-力迟滞曲线斜率变化；二是强度边界校核参数，包括支承座关键截面实测应力集中系数（通过贴片式应变计阵列获取）、导轨安装面边缘的微裂纹萌生状态（工业内窥镜+荧光渗透复查）、以及热处理区域硬度梯度分布（便携式里氏硬度仪沿轴向每50mm测三点）；三是关联性参数，如润滑脂成分衰变程度（红外光谱快检）和基座地脚螺栓预紧力离散度——这三类参数缺一不可，其中接触压痕深度和应力集中系数最具判别力，因前者直接反映界面刚度退化主因，后者能最早暴露局部强度裕度耗尽风险。</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>1个异常情况概要：导轨支承刚度下降但硬度检测合格。具体情况：便携硬度仪读数在标准范围内，但压痕深度超限，说明表面硬化层完好，但底层基体因微动磨损或残余应力松弛导致支撑刚度劣化。解决思路：不依赖硬度单指标，必须结合接触刚度测试（如静刚度加载-位移法）和支承座底面贴合率检测（蓝油法+数字图像比对），确认是否为界面间隙扩大所致。1个复杂问题概要：预紧螺栓扭矩衰减与支承刚度下降非线性耦合。具体问题：多个M12螺栓预紧力离散度达35%，导致局部支承刚度骤降，但整体平均扭矩仍满足下限，常规抽检易漏判。解决思路：采用螺栓群全数扭矩-转角双参数扫描，结合支承座底面应变云图反演载荷分布，识别低刚度区并针对性重紧+补充垫片，而非统一复拧。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>请简单说说，当工程图上标注的版本号更新后，BOM里对应零件的版本信息是否需要同步更新？为什么？</t>
+          <t>R4-Q018</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>需要同步更新。因为BOM是制造和装配的执行依据，其版本信息必须与最新生效的工程图保持严格一致；图纸版本变更意味着设计状态发生正式变更，若BOM未同步，会导致采购、加工、装配使用错误状态的零件，引发质量偏差或装配干涉。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>目前主流有三种同步方式：一是由设计工程师在PLM系统中发起ECN流程，自动触发BOM版本更新，时效性高、追溯性强，但依赖系统权限配置和流程闭环；二是由工艺或BOM工程师人工核对图纸版本后手动维护，灵活性强但易漏改、难留痕；三是在图纸发布时嵌入BOM校验规则，系统自动比对并预警差异，能提前拦截问题，但需前期定义清晰的版本映射逻辑。综合来看，第一种方式最稳妥，它把版本同步纳入设计变更受控流程，既满足时效性要求，又保障了从设计到制造的数据链完整性和责任可追溯性。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1个异常情况概要：图纸版本已更新但ECN流程未关闭，BOM系统仍沿用旧版本。具体情况：设计人员完成图纸升版后未及时提交ECN，或ECN审批卡在某环节，导致BOM未触发更新。解决思路：在PLM中设置图纸发布与ECN状态联动校验，未关联有效ECN的图纸禁止进入下发环节，并向设计责任人推送待办提醒。1个复杂问题概要：同一零件在多份图纸中存在不同版本引用。具体情况：该零件既是A部件的子件，又作为标准件被B、C部件调用，而各部件图纸版本更新节奏不一致，造成BOM中该零件出现多个版本标识冲突。解决思路：以零件主数据为唯一源头，强制所有图纸引用统一版本号，BOM仅继承主数据版本，图纸端通过‘引用版本锁定’机制明确所用状态，避免跨部件版本漂移。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>设计变更表达</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>图纸版本与BOM一致性</t>
+          <t>尺寸链分析</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>极值法公差叠加逻辑</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某精密齿轮箱的输出轴端跳动超差，该跳动由箱体轴承孔位置度、轴承外圈配合面圆柱度、轴承内圈与轴配合面同轴度、以及轴肩端面垂直度四个要素共同影响。请简述你如何运用极值法公差叠加逻辑，识别其中对封闭环跳动贡献最大的尺寸环，并说明在不增加检测成本的前提下，应优先收紧哪个环的公差及其工程依据。</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>极值法公差叠加是把各组成环公差按最不利方向线性相加，得到封闭环最大可能偏差的方法。它不考虑概率分布，只关注设计允许的极限组合。题干中封闭环是输出轴端跳动，四个组成环分别是箱体轴承孔位置度、轴承外圈配合面圆柱度、轴承内圈与轴配合面同轴度、轴肩端面垂直度——这四个环的偏差方向若全部朝同一侧叠加，就会导致端跳动达到理论最大值。</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>实际工作中常用三种分析方式：一是基于装配顺序做矢量分解，把每个环在跳动敏感方向的投影量化；二是用实物测量数据反推各环贡献占比，比如分别单件复测再组装验证；三是借助公差分析软件做极值敏感度排序。第一种最依赖经验但无需额外设备；第二种最可靠但耗时长；第三种效率高但需建模基础。综合来看，在不增加检测成本前提下，首选第一种——通过结构刚度和装配约束判断各环在径向跳动方向的实际传递效率，例如轴承外圈配合面圆柱度直接影响外圈变形后对内圈的偏斜传递，而轴肩端面垂直度主要影响轴向定位，对径向跳动的耦合效应较弱。</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>1个异常情况概要：轴承外圈配合面圆柱度实测合格但装入箱体后跳动仍超差。具体情况：箱体轴承孔刚性不足，压装时局部挤压导致外圈椭圆化，原圆柱度检测未模拟装配应力状态。解决思路：改用带预紧力的模拟工装检测，或在工艺文件中明确压装力与保压时间控制要求。1个复杂问题概要：四个组成环公差均在图纸范围内，但整机跳动仍不稳定。具体问题：轴承内圈与轴配合面同轴度受热装工艺波动影响大，冷态合格、热态装配后因温差收缩不均引发微偏心。解决思路：将该环公差收紧一级，并在作业指导书中固化加热温度、轴向压入速度和冷却静置时长三个关键参数。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>某机械产品在量产前完成最后一次设计冻结，工程图已签发A4版，对应BOM也已完成归档。后续发现其中一标准件的供应商型号变更，仅影响采购属性而不改变接口与功能。这种情况下，是否需要同步更新工程图版本号和BOM版本号？请简述理由。</t>
+          <t>R4-Q019</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>不需要更新工程图版本号，但必须更新BOM版本号。因为工程图表达的是结构、尺寸、公差、材料、表面处理等设计意图，该变更未引起任何几何、配合、强度或装配关系变化；而BOM是采购执行依据，供应商型号属于BOM的关键采购属性，型号变更即构成BOM数据项的有效性更新，必须通过版本升版确保采购信息可追溯、防错。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>常见处理方案有三种：一是仅修订BOM并升版，工程图维持A4不变——时效快、责任界面清晰、符合设计冻结原则，是首选；二是对工程图增加‘供应商备注栏’并局部修订，但不升版——易引发图纸有效性争议，且多数企业PLM系统不支持非版本化变更记录，存在合规风险；三是同步升版工程图和BOM——虽形式统一，但触发全套图纸会签与审批流程，延误量产节奏，且无技术必要性。综合权衡时效性、合规性与工程责任，第一种方案最优。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1个异常情况概要：BOM升版后，旧版BOM仍在采购系统中被误用。具体情况：采购员未及时同步新版BOM，按A4版BOM下单导致到货型号不符，引发产线停线。解决思路：在BOM升版时强制关联采购系统接口校验，并设置旧版BOM自动失效机制，同时要求工艺工程师在首件确认环节核对实物型号与当前BOM版本一致性。1个复杂问题概要：同一标准件在不同整机BOM中由不同供应商供货，但共用同一张工程图。具体问题：工程图未体现供应商差异，现场装配时混用导致批次管理失效或售后追溯困难。解决思路：在工程图技术要求栏以‘注：本件按BOM版本对应供应商执行’作统一说明，禁止在图纸上标注具体供应商型号，所有供应信息严格管控在BOM层级，确保图纸通用性与BOM专属性分离。</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>设计变更表达</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>图纸版本与BOM一致性</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>请简单说说，当工程图上标注的版本号更新后，BOM里对应零件的版本信息是否需要同步更新？为什么？</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>需要同步更新。因为BOM是制造和装配的执行依据，其版本信息必须与最新生效的工程图保持严格一致；图纸版本变更意味着设计状态发生正式变更，若BOM未同步，会导致采购、加工、装配使用错误状态的零件，引发质量偏差或装配干涉。</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>目前主流有三种同步方式：一是由设计工程师在PLM系统中发起ECN流程，自动触发BOM版本更新，时效性高、追溯性强，但依赖系统权限配置和流程闭环；二是由工艺或BOM工程师人工核对图纸版本后手动维护，灵活性强但易漏改、难留痕；三是在图纸发布时嵌入BOM校验规则，系统自动比对并预警差异，能提前拦截问题，但需前期定义清晰的版本映射逻辑。综合来看，第一种方式最稳妥，它把版本同步纳入设计变更受控流程，既满足时效性要求，又保障了从设计到制造的数据链完整性和责任可追溯性。</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>1个异常情况概要：图纸版本已更新但ECN流程未关闭，BOM系统仍沿用旧版本。具体情况：设计人员完成图纸升版后未及时提交ECN，或ECN审批卡在某环节，导致BOM未触发更新。解决思路：在PLM中设置图纸发布与ECN状态联动校验，未关联有效ECN的图纸禁止进入下发环节，并向设计责任人推送待办提醒。1个复杂问题概要：同一零件在多份图纸中存在不同版本引用。具体情况：该零件既是A部件的子件，又作为标准件被B、C部件调用，而各部件图纸版本更新节奏不一致，造成BOM中该零件出现多个版本标识冲突。解决思路：以零件主数据为唯一源头，强制所有图纸引用统一版本号，BOM仅继承主数据版本，图纸端通过‘引用版本锁定’机制明确所用状态，避免跨部件版本漂移。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>当一张装配图的修订版本号从A2升至A3，且其中某个零件的结构发生变更，但该零件在BOM中仍显示为旧版本号，此时应依据什么关键信息来判断BOM是否需要同步更新？请简述判断依据。</t>
+          <t>R4-Q020</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>应依据该零件结构变更是否导致其功能、装配关系、接口尺寸、公差配合或可制造性发生实质性变化。只要变更影响到零件在整机中的物理安装、运动约束、载荷传递、密封/连接可靠性或后续加工检测方式，BOM就必须同步更新版本号。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>常见判断方法有四种：一是查设计变更单——核对ECN中是否明确标注‘影响BOM’及‘需更新物料主数据’，时效快但依赖流程执行质量；二是比对A2与A3版图纸的关键视图和尺寸表——重点看定位孔、配合面、螺纹规格、形位公差框格变化，全面但耗时；三是调取PLM系统中的变更影响分析报告——自动识别关联部件与工艺路线变动，准确度高且支持批量校验；四是现场确认首件装配状态——通过试装验证干涉、间隙、紧固力是否异常，最贴近实际但滞后于设计发布。综合来看，以PLM系统影响分析为主、设计变更单为辅、关键图纸比对为验证手段，是当前制造业机械工程师最常用且兼顾时效性与完整性的组合方案。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1个异常情况概要：BOM版本未更新但生产已领用新结构零件。具体情况：车间按A3版图纸加工了变更后的零件，但仓库仍按旧BOM发料，导致装配时发现孔位偏移或螺栓无法穿入。解决思路：立即冻结该批次零件流转，由机械工程师牵头组织设计、工艺、质量三方会签《临时替代评审单》，明确使用边界，并同步在PLM中补录BOM变更并反向触发库存批次标识。1个复杂问题概要：结构变更仅涉及非关键表面特征，但引发下游焊接夹具定位基准失效。具体问题：零件某处倒角微调未改标注尺寸，却使夹具定位销无法完全插入，造成批量焊偏。解决思路：机械工程师须联合工艺工程师复核所有工装适配性，将此类‘隐性影响’纳入BOM变更强制审查项，并在ECN审批节点增加‘工艺可行性会签’环节。</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>设计变更表达</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>图纸版本与BOM一致性</t>
+          <t>工程图表达</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>技术要求与图面信息一致性</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某泵体铸件图纸中，主视图标注了Φ80H7孔的尺寸与公差，侧视图上该孔对应位置却以‘Φ80’无公差形式表达，且技术要求栏注明‘未注公差按GB/T 1800.2—2020中IT12执行’。若实测孔径为Φ80.15，符合IT12（±0.22）但超出H7（+0.021/0）范围，该尺寸是否合格？请从图面视图间信息冲突时的优先级规则和标准条款适用逻辑说明判断依据。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>该尺寸不合格。工程图中，同一要素在不同视图上出现尺寸标注冲突时，以明确标注公差的视图为优先；主视图已给出Φ80H7，属于有公差的正式尺寸，其要求直接覆盖侧视图的无公差简化表达；技术要求中‘未注公差按IT12执行’仅适用于图中完全未标注公差的尺寸，不适用于已有H7标注的同一要素。</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>实际工作中常用三种处理方式：一是以主视图H7为准，直接拒收超差件，响应快、责任清晰，但可能造成批量返工；二是组织设计、工艺、质量三方会签确认是否可放宽，兼顾技术严谨性与生产连续性，但耗时较长；三是核查原始设计意图，比如调阅数模或设计变更单，确认侧视图省略公差是否属制图疏漏，这是最根本的解决路径。综合来看，第三种方式最优——既守住图纸作为制造依据的法律效力，又避免将制图表达问题误判为加工质量问题。</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>1个异常情况概要：设计人员在多视图中对同一尺寸采用不一致标注，且未加注说明。具体情况：侧视图省略公差是常见绘图习惯，但未同步删除或屏蔽该处尺寸，导致现场误读。解决思路：严格执行企业《机械制图审核清单》，要求所有投图前必须进行‘同要素跨视图公差一致性’专项检查。1个复杂问题概要：H7孔实际用于装配动密封，但检测时仅按尺寸判定合格，忽略形位公差与表面粗糙度联动影响。具体问题：Φ80.15虽超H7上限，但若圆度、圆柱度良好且表面无毛刺，可能仍满足泵体低压工况下的密封功能。解决思路：启动基于功能需求的‘尺寸-形位-表面’协同放行评估，由机械工程师牵头，联合密封设计与工艺人员共同签署临时使用意见，并同步推动图纸升版。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>某量产产品在客户端发生装配干涉，经追溯发现：设计部门已发布新版零件图，将关键配合面的平面度公差从严调整为0.02mm，但BOM中该零件仍引用旧版图号，且ERP系统未触发版本校验告警。你如何从设计变更发起、BOM维护、生产执行三个环节，构建防错机制来保障图纸版本与BOM的一致性？请简述核心控制逻辑。</t>
+          <t>R4-Q022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>图纸版本与BOM一致性，是指在设计变更生效后，BOM中所引用的图号必须与当前受控发布的有效图纸版本严格对应，且该对应关系需在变更发起、BOM更新、生产领料三个节点形成闭环校验，不得存在图号滞后、图号跳变或系统无感知等断点。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>常见方案有四种：一是设计变更单强制绑定图号+ERP自动校验字段，优点是源头强约束、响应快，缺点是依赖ERP配置深度，部分老系统不支持图号字段级比对；二是BOM审批流嵌入图纸版本核对清单，由工艺和制造代表会签，覆盖全面但时效性弱；三是PLM与ERP建立图号-物料主数据双向映射并设置变更联动锁，目前主流落地效果最好，兼顾自动化与可追溯；四是现场工位扫码调取最新图纸版本并比对BOM图号，属于执行端兜底，但无法预防错误下发。综合来看，第三种方案最合理——它把图号作为物料主数据的关键属性，在设计变更提交时即锁定新图号与旧图号差异，在BOM生效前触发版本冲突提示，且不增加人工干预环节。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1个异常情况概要：设计变更单已归档，但BOM未同步更新图号，仅修改了描述字段。具体情况：工程师为赶进度，在PLM中仅更新了变更说明，未实际替换BOM行项目中的图号引用，导致ERP读取的仍是旧图号。解决思路：在PLM变更流程中设置‘图号字段不可为空且必须变更’的硬性校验规则，并与ERP接口做图号字符串级比对，不一致则阻断BOM发布。1个复杂问题概要：同一零件多版本并存于产线，旧图号零件尚未消耗完，新图号已启用。具体问题：BOM虽已更新，但仓库按旧图号发料，装配现场无法识别图纸版本差异，导致混装。解决思路：在BOM中增设‘图号有效期起止日期’字段，与批次管理联动，ERP按领料日期自动匹配应发图号，并在工单打印页突出显示当批适用图号及关键公差变更项。</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>设计变更表达</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>图纸版本与BOM一致性</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>困难</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某机械产品在量产前完成最后一次设计冻结，工程图已签发A4版，对应BOM也已完成归档。后续发现其中一标准件的供应商型号变更，仅影响采购属性而不改变接口与功能。这种情况下，是否需要同步更新工程图版本号和BOM版本号？请简述理由。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>不需要更新工程图版本号，但必须更新BOM版本号。因为工程图表达的是结构、尺寸、公差、材料、表面处理等设计意图，该变更未引起任何几何、配合、强度或装配关系变化；而BOM是采购执行依据，供应商型号属于BOM的关键采购属性，型号变更即构成BOM数据项的有效性更新，必须通过版本升版确保采购信息可追溯、防错。</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>常见处理方案有三种：一是仅修订BOM并升版，工程图维持A4不变——时效快、责任界面清晰、符合设计冻结原则，是首选；二是对工程图增加‘供应商备注栏’并局部修订，但不升版——易引发图纸有效性争议，且多数企业PLM系统不支持非版本化变更记录，存在合规风险；三是同步升版工程图和BOM——虽形式统一，但触发全套图纸会签与审批流程，延误量产节奏，且无技术必要性。综合权衡时效性、合规性与工程责任，第一种方案最优。</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>1个异常情况概要：BOM升版后，旧版BOM仍在采购系统中被误用。具体情况：采购员未及时同步新版BOM，按A4版BOM下单导致到货型号不符，引发产线停线。解决思路：在BOM升版时强制关联采购系统接口校验，并设置旧版BOM自动失效机制，同时要求工艺工程师在首件确认环节核对实物型号与当前BOM版本一致性。1个复杂问题概要：同一标准件在不同整机BOM中由不同供应商供货，但共用同一张工程图。具体问题：工程图未体现供应商差异，现场装配时混用导致批次管理失效或售后追溯困难。解决思路：在工程图技术要求栏以‘注：本件按BOM版本对应供应商执行’作统一说明，禁止在图纸上标注具体供应商型号，所有供应信息严格管控在BOM层级，确保图纸通用性与BOM专属性分离。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>在批量生产中，某钣金零件多次折弯后实际尺寸与展开图不符，但单道折弯验证合格。请简述此时最应优先核查的展开约束相关因素。</t>
+          <t>R4-Q023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>此时最应优先核查的是多道折弯叠加过程中，材料中性层偏移的累积效应、各折弯工序间定位基准的传递误差，以及折弯回弹在连续成形中的非线性叠加规律——这三者共同构成钣金展开在批量多工步成形下的核心约束条件。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>第一种方案是复核展开补偿系数是否按多折弯路径重新标定：它时效快、无需改模具，但仅适用于回弹规律稳定的材料和折弯顺序；第二种是引入分段式工艺基准设计，在关键折弯后增设辅助定位孔或止口，能有效抑制误差传递，但需增加冲孔工步和检测点；第三种是采用基于实测数据的折弯顺序逆向优化，通过试模反馈动态调整展开余量分配，覆盖全面且适配性强，是当前主流产线首选。综合来看，第三种方法在保证首件验证周期可控的前提下，兼顾了工艺鲁棒性和长期稳定性。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1个异常情况概要：折弯顺序变更后首件合格但批量尺寸漂移；具体情况：同一展开图用于不同折弯机或不同操作员时，因压痕深度、下模V口宽度微差导致每道回弹量波动，多道叠加后超差；解决思路：锁定主控折弯参数组合（如上模圆角、下模开口、折弯速度），并将其纳入工艺卡受控项。1个复杂问题概要：U形件两侧对称折弯后底边长度缩短超差；具体问题：第二道折弯引发已成形边的弹性压缩与局部塑性畸变，使中性层整体内移，传统单道补偿失效；解决思路：在展开图底边处预加拉伸余量，并在工艺文件中明确该余量仅适用于三折及以上闭合类结构，由工艺工程师会签确认。</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>制造工艺</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>钣金工艺</t>
+          <t>工程图与公差</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>钣金展开约束</t>
+          <t>设计变更表达</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>图纸版本与BOM一致性</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>当一张装配图的修订版本号从A2升至A3，且其中某个零件的结构发生变更，但该零件在BOM中仍显示为旧版本号，此时应依据什么关键信息来判断BOM是否需要同步更新？请简述判断依据。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>应依据该零件结构变更是否导致其功能、装配关系、接口尺寸、公差配合或可制造性发生实质性变化。只要变更影响到零件在整机中的物理安装、运动约束、载荷传递、密封/连接可靠性或后续加工检测方式，BOM就必须同步更新版本号。</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>常见判断方法有四种：一是查设计变更单——核对ECN中是否明确标注‘影响BOM’及‘需更新物料主数据’，时效快但依赖流程执行质量；二是比对A2与A3版图纸的关键视图和尺寸表——重点看定位孔、配合面、螺纹规格、形位公差框格变化，全面但耗时；三是调取PLM系统中的变更影响分析报告——自动识别关联部件与工艺路线变动，准确度高且支持批量校验；四是现场确认首件装配状态——通过试装验证干涉、间隙、紧固力是否异常，最贴近实际但滞后于设计发布。综合来看，以PLM系统影响分析为主、设计变更单为辅、关键图纸比对为验证手段，是当前制造业机械工程师最常用且兼顾时效性与完整性的组合方案。</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>1个异常情况概要：BOM版本未更新但生产已领用新结构零件。具体情况：车间按A3版图纸加工了变更后的零件，但仓库仍按旧BOM发料，导致装配时发现孔位偏移或螺栓无法穿入。解决思路：立即冻结该批次零件流转，由机械工程师牵头组织设计、工艺、质量三方会签《临时替代评审单》，明确使用边界，并同步在PLM中补录BOM变更并反向触发库存批次标识。1个复杂问题概要：结构变更仅涉及非关键表面特征，但引发下游焊接夹具定位基准失效。具体问题：零件某处倒角微调未改标注尺寸，却使夹具定位销无法完全插入，造成批量焊偏。解决思路：机械工程师须联合工艺工程师复核所有工装适配性，将此类‘隐性影响’纳入BOM变更强制审查项，并在ECN审批节点增加‘工艺可行性会签’环节。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>当同一零件在多个总成中复用，且各总成的设计变更节奏不同——例如A总成已升级至第5版图纸并更新了位置度基准，而B总成仍使用第3版图纸且BOM未标注版本差异——你如何识别这种跨BOM版本混用风险，并在不增加人工核对负担的前提下，确保工艺、质检和供应商交付依据唯一有效版本？请说明技术路径和落地要点。</t>
+          <t>R4-Q024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>图纸版本与BOM一致性，是指同一零件在不同总成BOM中引用的图纸版本号必须与该总成当前生效的设计状态严格对应；当BOM未显式标注图纸版本、或多个总成共用同一零件号但引用不同版本图纸时，即构成版本混用风险，直接导致工艺编制、尺寸检测基准、供应商来料验收依据不统一。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>目前主流有三种技术路径：一是BOM系统嵌入图纸版本字段并强制关联ECN闭环，优势是源头受控、可追溯，但依赖设计端严格执行版本标注；二是PLM系统建立‘零件-总成’双向版本映射视图，自动标红跨版本引用，优势是可视化强、无需人工比对，但需配置规则引擎识别基准变更影响；三是MES/QMS端部署轻量级版本校验插件，在下发工艺卡和检验规程前自动抓取当前总成ECN状态匹配图纸版本，优势是不改变前端流程、落地快。综合来看，第二种最全面——它既覆盖设计发布环节，又支撑制造执行环节，且能识别位置度基准变更这类关键公差要素的版本敏感性，时效性满足产线节拍。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1个异常情况概要：BOM冻结后设计补发ECN但未同步更新BOM版本字段。具体情况：B总成BOM已冻结用于量产，设计私下补发第3版图纸的局部修改单（未走正式ECN），导致工艺按旧图加工、质检按新图验收冲突。解决思路：在PLM中设置BOM冻结锁，任何图纸变更必须触发BOM版本升版或备注说明豁免项，否则无法发布到制造系统。1个复杂问题概要：同一零件在A总成中因刚度要求收紧位置度公差并变更基准，在B总成中因装配空间限制仍沿用宽松公差。具体问题：供应商按单一图纸供货，无法同时满足两套基准和公差要求。解决思路：在零件主数据中拆分‘设计状态标识’字段（如‘A态’‘B态’），在BOM层级绑定对应态的图纸与检验特性，使工艺和质检系统自动调取匹配态的作业依据。</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>设计变更表达</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>图纸版本与BOM一致性</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某量产产品在客户端发生装配干涉，经追溯发现：设计部门已发布新版零件图，将关键配合面的平面度公差从严调整为0.02mm，但BOM中该零件仍引用旧版图号，且ERP系统未触发版本校验告警。你如何从设计变更发起、BOM维护、生产执行三个环节，构建防错机制来保障图纸版本与BOM的一致性？请简述核心控制逻辑。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>图纸版本与BOM一致性，是指在设计变更生效后，BOM中所引用的图号必须与当前受控发布的有效图纸版本严格对应，且该对应关系需在变更发起、BOM更新、生产领料三个节点形成闭环校验，不得存在图号滞后、图号跳变或系统无感知等断点。</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>常见方案有四种：一是设计变更单强制绑定图号+ERP自动校验字段，优点是源头强约束、响应快，缺点是依赖ERP配置深度，部分老系统不支持图号字段级比对；二是BOM审批流嵌入图纸版本核对清单，由工艺和制造代表会签，覆盖全面但时效性弱；三是PLM与ERP建立图号-物料主数据双向映射并设置变更联动锁，目前主流落地效果最好，兼顾自动化与可追溯；四是现场工位扫码调取最新图纸版本并比对BOM图号，属于执行端兜底，但无法预防错误下发。综合来看，第三种方案最合理——它把图号作为物料主数据的关键属性，在设计变更提交时即锁定新图号与旧图号差异，在BOM生效前触发版本冲突提示，且不增加人工干预环节。</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>1个异常情况概要：设计变更单已归档，但BOM未同步更新图号，仅修改了描述字段。具体情况：工程师为赶进度，在PLM中仅更新了变更说明，未实际替换BOM行项目中的图号引用，导致ERP读取的仍是旧图号。解决思路：在PLM变更流程中设置‘图号字段不可为空且必须变更’的硬性校验规则，并与ERP接口做图号字符串级比对，不一致则阻断BOM发布。1个复杂问题概要：同一零件多版本并存于产线，旧图号零件尚未消耗完，新图号已启用。具体问题：BOM虽已更新，但仓库按旧图号发料，装配现场无法识别图纸版本差异，导致混装。解决思路：在BOM中增设‘图号有效期起止日期’字段，与批次管理联动，ERP按领料日期自动匹配应发图号，并在工单打印页突出显示当批适用图号及关键公差变更项。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>请简单说说，为什么在钣金折弯时，通常要让折弯内半径不小于材料厚度？</t>
+          <t>R4-Q025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>这是为了防止折弯过程中材料内侧出现裂纹或过度减薄。当内半径过小，金属纤维在弯曲内侧被剧烈压缩和挤压，超出材料在冷态下的塑性变形能力，容易引发微观开裂或表面压痕；同时外侧拉伸加剧，可能导致断面局部颈缩，影响后续装配定位和结构承载连续性。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>目前主流有三种控制方式：一是按材料厚度直接设定最小内半径，比如普通碳钢取t、不锈钢取1.2t，兼顾通用性与工艺容错；二是采用带预压痕的V槽模具配合数控折弯机，通过控制下模开口和上模圆角实现稳定成形，适合中小批量但对模具精度依赖高；三是使用滚压折弯或分段折弯工艺处理厚板或高强钢，可降低单次变形量，但设备成本高、编程复杂。综合来看，第一种方式最常用——它在保证折弯合格率的前提下，最大程度兼容现有产线设备、缩短编程调试时间，也便于图纸标注和检验人员现场比对。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1个异常情况概要：折弯后内侧出现细微纵向裂纹。具体情况：某Q235B板材厚度2mm，按图样要求折弯内半径R1.5，实际折弯后内圆角处出现肉眼可见的浅表裂纹。解决思路：立即停用该模具参数，复核材料实测厚度与力学性能（尤其延伸率），改用R2.0内半径重试，并检查折弯方向是否垂直于材料轧制方向。1个复杂问题概要：同一零件多道折弯中，后序折弯导致前序折弯圆角回弹超差。具体问题：某机箱侧板需四边折弯，第三边折弯后，首边已成形的R2.0圆角实测变为R2.4，影响盖板插装间隙。解决思路：在工艺规划阶段预留回弹补偿量，优先安排长边先折、短边后折，并在首道折弯后增加校平工序；必要时改用带角度反馈的伺服折弯机进行闭环补偿。</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>制造工艺</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>钣金工艺</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>折弯半径选择</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>钣金展开约束</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>在批量生产中，某钣金零件多次折弯后实际尺寸与展开图不符，但单道折弯验证合格。请简述此时最应优先核查的展开约束相关因素。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>此时最应优先核查的是多道折弯叠加过程中，材料中性层偏移的累积效应、各折弯工序间定位基准的传递误差，以及折弯回弹在连续成形中的非线性叠加规律——这三者共同构成钣金展开在批量多工步成形下的核心约束条件。</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>第一种方案是复核展开补偿系数是否按多折弯路径重新标定：它时效快、无需改模具，但仅适用于回弹规律稳定的材料和折弯顺序；第二种是引入分段式工艺基准设计，在关键折弯后增设辅助定位孔或止口，能有效抑制误差传递，但需增加冲孔工步和检测点；第三种是采用基于实测数据的折弯顺序逆向优化，通过试模反馈动态调整展开余量分配，覆盖全面且适配性强，是当前主流产线首选。综合来看，第三种方法在保证首件验证周期可控的前提下，兼顾了工艺鲁棒性和长期稳定性。</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>1个异常情况概要：折弯顺序变更后首件合格但批量尺寸漂移；具体情况：同一展开图用于不同折弯机或不同操作员时，因压痕深度、下模V口宽度微差导致每道回弹量波动，多道叠加后超差；解决思路：锁定主控折弯参数组合（如上模圆角、下模开口、折弯速度），并将其纳入工艺卡受控项。1个复杂问题概要：U形件两侧对称折弯后底边长度缩短超差；具体问题：第二道折弯引发已成形边的弹性压缩与局部塑性畸变，使中性层整体内移，传统单道补偿失效；解决思路：在展开图底边处预加拉伸余量，并在工艺文件中明确该余量仅适用于三折及以上闭合类结构，由工艺工程师会签确认。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>某输送机支架图纸中，角焊缝符号的基准线带虚线，虚线侧标注‘5’，实线侧无数字，箭头指向T型接头的立板。请简述该符号表明焊缝实际施焊在哪一侧，以及为何虚线侧的尺寸值直接决定了受力焊脚的有效高度。</t>
+          <t>R4-Q026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>该焊缝符号表示焊缝仅施焊在虚线侧，也就是T型接头中腹板（立板）与翼板（底板）相交的、远离箭头所指方向的那一侧；虚线侧标注的‘5’代表焊脚尺寸为5毫米，这个数值就是焊缝在受力状态下实际参与承载的有效焊脚高度。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>在输送机支架这类承载动载荷的结构件上，常见三种执行方案：一是按符号单侧施焊并严格控制焊脚5毫米，兼顾强度与热变形；二是双侧对称焊但未修改符号，虽减小变形但易引发图纸与实物不符的质量争议；三是焊后打磨修形补偿尺寸偏差，但会削弱热影响区性能且增加工时。最优方案是第一种——严格依图单侧施焊，并在工艺文件中明确标注‘仅虚线侧成型，实线侧不焊’，配合首件三坐标抽检焊脚高度与位置。该方案时效性好、责任界面清晰，符合机械工程师对图纸执行力和过程可控性的核心要求。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1个异常情况概要：焊缝实际焊脚高度普遍偏小，仅3.8～4.2毫米。具体情况：焊工为避免立板烧穿而主动减小电流或加快速度，导致熔深不足。解决思路：在焊接工艺卡中增设‘最小焊脚验证点’，要求每班首件用焊缝量规实测，并记录于巡检表；同步调整夹具定位，使立板与底板间隙控制在1.5毫米以内以稳定熔池形态。1个复杂问题概要：支架服役中立板根部出现疲劳裂纹。具体问题：焊缝有效截面不足叠加T型接头应力集中，导致5毫米焊脚在反复冲击载荷下提前失效。解决思路：联合结构工程师复核局部应力，若确认承载裕度不足，则在图纸升版中将该焊缝改为‘双侧5毫米角焊缝’，并在工艺文件中增加‘立板背面清根后封底焊’工序，确保全截面连续承载。</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>制造工艺</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>焊接工艺</t>
+          <t>工程图与公差</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>焊缝符号表达</t>
+          <t>设计变更表达</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>图纸版本与BOM一致性</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>当同一零件在多个总成中复用，且各总成的设计变更节奏不同——例如A总成已升级至第5版图纸并更新了位置度基准，而B总成仍使用第3版图纸且BOM未标注版本差异——你如何识别这种跨BOM版本混用风险，并在不增加人工核对负担的前提下，确保工艺、质检和供应商交付依据唯一有效版本？请说明技术路径和落地要点。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>图纸版本与BOM一致性，是指同一零件在不同总成BOM中引用的图纸版本号必须与该总成当前生效的设计状态严格对应；当BOM未显式标注图纸版本、或多个总成共用同一零件号但引用不同版本图纸时，即构成版本混用风险，直接导致工艺编制、尺寸检测基准、供应商来料验收依据不统一。</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>目前主流有三种技术路径：一是BOM系统嵌入图纸版本字段并强制关联ECN闭环，优势是源头受控、可追溯，但依赖设计端严格执行版本标注；二是PLM系统建立‘零件-总成’双向版本映射视图，自动标红跨版本引用，优势是可视化强、无需人工比对，但需配置规则引擎识别基准变更影响；三是MES/QMS端部署轻量级版本校验插件，在下发工艺卡和检验规程前自动抓取当前总成ECN状态匹配图纸版本，优势是不改变前端流程、落地快。综合来看，第二种最全面——它既覆盖设计发布环节，又支撑制造执行环节，且能识别位置度基准变更这类关键公差要素的版本敏感性，时效性满足产线节拍。</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>1个异常情况概要：BOM冻结后设计补发ECN但未同步更新BOM版本字段。具体情况：B总成BOM已冻结用于量产，设计私下补发第3版图纸的局部修改单（未走正式ECN），导致工艺按旧图加工、质检按新图验收冲突。解决思路：在PLM中设置BOM冻结锁，任何图纸变更必须触发BOM版本升版或备注说明豁免项，否则无法发布到制造系统。1个复杂问题概要：同一零件在A总成中因刚度要求收紧位置度公差并变更基准，在B总成中因装配空间限制仍沿用宽松公差。具体问题：供应商按单一图纸供货，无法同时满足两套基准和公差要求。解决思路：在零件主数据中拆分‘设计状态标识’字段（如‘A态’‘B态’），在BOM层级绑定对应态的图纸与检验特性，使工艺和质检系统自动调取匹配态的作业依据。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>某法兰盘零件原设计使用45号钢调质处理，现为减重改用7075-T6铝合金锻件。除材料本身价格差异外，该变更对机加工阶段的夹具适配性和单件装夹耗时通常会产生怎样的影响？请简述原因。</t>
+          <t>R4-Q027</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>材料由45号钢调质改为7075-T6铝合金后，夹具适配性通常会下降，单件装夹耗时普遍增加。主要原因是：7075-T6铝合金强度高、刚度低、热膨胀系数大、表面硬度低且易产生压痕，导致原有钢件夹具的夹紧力、定位面匹配性、支撑刚性不再适用；同时因材料软、易变形，需降低夹紧力并增加辅助支撑点，操作步骤变多。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>常见应对方案有四种：一是改造现有夹具，在定位面加装铜或聚氨酯缓冲垫，并缩小夹紧行程，优点是成本低、周期短，但重复定位精度易波动；二是采用模块化快换夹具，通过可调支撑钉和气动柔性夹紧，适配不同刚度工件，初期投入高但长期换型效率好；三是改用真空吸盘+边缘机械夹持组合，适合大平面法兰，但对零件底面平面度和清洁度要求严，现场维护频次高；四是重新设计专用铝合金夹具，整体刚性强化、接触面积增大、夹紧力分布更均匀，综合稳定性最好，是当前批量生产中最推荐的方案。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1个异常情况概要：夹具未调整即直接装夹7075-T6件，导致法兰盘内孔基准面被压塌或产生肉眼不可见的弹性凹陷；具体情况是后续精镗工序出现尺寸超差、圆度突变，首件检验合格但批量加工中段开始失稳；解决思路是强制执行新材料首件夹装验证流程，用三坐标比对夹紧前后基准面形变量，确认夹紧力阈值并固化在作业指导书中。1个复杂问题概要：同一套夹具需混产钢件与铝合金件，切换频繁；具体问题是夹具状态记忆缺失，操作人员凭经验调整易出错，造成批次性装夹不良；解决思路是在夹具本体集成机械式状态标识销+数字工单扫码联动提示，由班组长在MES系统中确认夹具配置状态后方可开工，把人为判断转为防错机制。</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>制造工艺</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>制造成本评估</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>材料成本影响</t>
+          <t>钣金工艺</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>折弯半径选择</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>请简单说说，为什么在钣金折弯时，通常要让折弯内半径不小于材料厚度？</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>这是为了防止折弯过程中材料内侧出现裂纹或过度减薄。当内半径过小，金属纤维在弯曲内侧被剧烈压缩和挤压，超出材料在冷态下的塑性变形能力，容易引发微观开裂或表面压痕；同时外侧拉伸加剧，可能导致断面局部颈缩，影响后续装配定位和结构承载连续性。</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>目前主流有三种控制方式：一是按材料厚度直接设定最小内半径，比如普通碳钢取t、不锈钢取1.2t，兼顾通用性与工艺容错；二是采用带预压痕的V槽模具配合数控折弯机，通过控制下模开口和上模圆角实现稳定成形，适合中小批量但对模具精度依赖高；三是使用滚压折弯或分段折弯工艺处理厚板或高强钢，可降低单次变形量，但设备成本高、编程复杂。综合来看，第一种方式最常用——它在保证折弯合格率的前提下，最大程度兼容现有产线设备、缩短编程调试时间，也便于图纸标注和检验人员现场比对。</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>1个异常情况概要：折弯后内侧出现细微纵向裂纹。具体情况：某Q235B板材厚度2mm，按图样要求折弯内半径R1.5，实际折弯后内圆角处出现肉眼可见的浅表裂纹。解决思路：立即停用该模具参数，复核材料实测厚度与力学性能（尤其延伸率），改用R2.0内半径重试，并检查折弯方向是否垂直于材料轧制方向。1个复杂问题概要：同一零件多道折弯中，后序折弯导致前序折弯圆角回弹超差。具体问题：某机箱侧板需四边折弯，第三边折弯后，首边已成形的R2.0圆角实测变为R2.4，影响盖板插装间隙。解决思路：在工艺规划阶段预留回弹补偿量，优先安排长边先折、短边后折，并在首道折弯后增加校平工序；必要时改用带角度反馈的伺服折弯机进行闭环补偿。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>在大批量生产齿轮类零件时，若将材料从20CrMnTi渗碳钢改为免热处理的新型非调质钢，这一变更对后续热处理工序的能耗成本和设备占用时间会产生什么直接影响？请简述依据。</t>
+          <t>R4-Q035</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>直接影响是：热处理工序完全取消，能耗成本降为零，设备占用时间为零。依据在于，20CrMnTi必须经过渗碳+淬火+回火三道热处理才能满足齿面硬度与芯部韧性的匹配要求；而非调质钢通过钒/钛微合金化与控轧控冷工艺，在终轧后直接获得组织均匀的贝氏体+铁素体复相组织，出厂状态即满足齿轮常用强度级别（如σb≥800MPa、表面硬度HRC28～35），无需任何后续热处理。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>当前主流适配方案有三类：一是采用VN-Ti复合微合金化非调质钢（如F40MnV），控冷终轧后空冷即可，设备兼容现有热轧线，但需校核齿根弯曲疲劳寿命是否达标；二是选用含硫易切削型非调质钢（如38MnVS6），切削效率提升15%以上，但需评估齿面接触疲劳性能衰减风险；三是改用低碳贝氏体非调质钢（如BHS700），强韧性更优，但对终轧温度与冷却速率控制精度要求更高，产线需加装在线温度闭环监测模块。综合权衡批量稳定性、检测成本与产线改造幅度，第一类VN-Ti系方案在齿轮类中等模数（m=2～6）、中低载荷场景下工程落地性最强。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1个异常情况概要：非调质钢齿轮在精加工后出现齿形畸变超差。具体情况：因材料残余应力分布不均，滚齿或剃齿后齿向误差突增0.015mm以上，超出图纸公差带。解决思路：在粗车后增加一次600℃以下低温去应力退火，或改用双面同步铣齿替代单刃滚齿，降低切削力扰动。1个复杂问题概要：同批次非调质钢齿轮在台架耐久试验中发生早期齿面剥落。具体问题：非调质钢表层硬度梯度平缓，导致赫兹接触应力下次表层剪切应力峰值位置上移，加速微裂纹萌生。解决思路：在精加工后增加喷丸强化工序，引入表层压应力场，同时复核原设计齿廓修形量是否需增大0.01～0.02mm以改善载荷分布。</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>制造工艺</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>制造成本评估</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>材料成本影响</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某法兰盘零件原设计使用45号钢调质处理，现为减重改用7075-T6铝合金锻件。除材料本身价格差异外，该变更对机加工阶段的夹具适配性和单件装夹耗时通常会产生怎样的影响？请简述原因。</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>材料由45号钢调质改为7075-T6铝合金后，夹具适配性通常会下降，单件装夹耗时普遍增加。主要原因是：7075-T6铝合金强度高、刚度低、热膨胀系数大、表面硬度低且易产生压痕，导致原有钢件夹具的夹紧力、定位面匹配性、支撑刚性不再适用；同时因材料软、易变形，需降低夹紧力并增加辅助支撑点，操作步骤变多。</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>常见应对方案有四种：一是改造现有夹具，在定位面加装铜或聚氨酯缓冲垫，并缩小夹紧行程，优点是成本低、周期短，但重复定位精度易波动；二是采用模块化快换夹具，通过可调支撑钉和气动柔性夹紧，适配不同刚度工件，初期投入高但长期换型效率好；三是改用真空吸盘+边缘机械夹持组合，适合大平面法兰，但对零件底面平面度和清洁度要求严，现场维护频次高；四是重新设计专用铝合金夹具，整体刚性强化、接触面积增大、夹紧力分布更均匀，综合稳定性最好，是当前批量生产中最推荐的方案。</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>1个异常情况概要：夹具未调整即直接装夹7075-T6件，导致法兰盘内孔基准面被压塌或产生肉眼不可见的弹性凹陷；具体情况是后续精镗工序出现尺寸超差、圆度突变，首件检验合格但批量加工中段开始失稳；解决思路是强制执行新材料首件夹装验证流程，用三坐标比对夹紧前后基准面形变量，确认夹紧力阈值并固化在作业指导书中。1个复杂问题概要：同一套夹具需混产钢件与铝合金件，切换频繁；具体问题是夹具状态记忆缺失，操作人员凭经验调整易出错，造成批次性装夹不良；解决思路是在夹具本体集成机械式状态标识销+数字工单扫码联动提示，由班组长在MES系统中确认夹具配置状态后方可开工，把人为判断转为防错机制。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>请简述标准化降本中‘减少零部件种类’这一做法最直接的成本影响。</t>
+          <t>R4-Q036</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>最直接的成本影响是降低采购与仓储环节的固定管理成本，包括供应商协调、物料编码维护、库存盘点频次、安全库存设置和入库检验批次数量。因为每一种零件都需要独立的采购订单处理、入库验收记录、库位占用和周期性呆滞评估，种类减少后，这些事务性工作量呈非线性下降。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>在机械工程师日常工作中，实现零部件种类精简主要有四种路径：一是通过公差带合并，比如将原本按±0.1和±0.15分别管控的轴类件统一到±0.12公差带，在保证装配间隙和功能前提下减少规格；二是采用模块化接口替代专用连接结构，例如用标准M6内六角圆柱头螺钉+通用垫圈组合替代定制卡扣件；三是借用已有平台件，优先选用本企业已批量验证的轴承、紧固件或铸锻毛坯型号；四是推行断面标准化，对同类支架类零件统一厚度、倒角尺寸和安装孔分布模式。其中，公差带合并和模块化接口最常用，前者实施快但需校核实际装配干涉风险，后者长期效益高但需跨部门对齐接口定义，综合来看，优先采用模块化接口更稳妥，因其不牺牲结构刚度和装配重复性，且便于后期维护备件统一。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1个异常情况概要：同类零件合并后出现局部应力集中加剧。具体情况：某机架上原两种不同截面的加强筋板被统一为较厚型材，导致焊接热输入增大、焊缝根部残余应力升高，在振动工况下提前萌生微裂纹。解决思路：在合并前必须复核典型工况下的静刚度与模态响应，结合焊缝区域的几何突变系数做简化应力评估，必要时保留过渡段差异设计。1个复杂问题概要：跨产品线零件通用化引发装配兼容性冲突。具体问题：将A系列电机端盖的定位销孔位置套用于B系列，但B系列壳体铸造收缩率略高，导致销钉过盈配合失效、端盖偏摆超差。解决思路：以铸造材质、壁厚和冷却条件为约束，反向核定各系列毛坯关键尺寸的实测变异带宽，仅在变异交集区间内定义共用特征，而非简单按图纸尺寸对齐。</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t>制造工艺</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>制造成本评估</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>标准化降本</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>材料成本影响</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>在大批量生产齿轮类零件时，若将材料从20CrMnTi渗碳钢改为免热处理的新型非调质钢，这一变更对后续热处理工序的能耗成本和设备占用时间会产生什么直接影响？请简述依据。</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>直接影响是：热处理工序完全取消，能耗成本降为零，设备占用时间为零。依据在于，20CrMnTi必须经过渗碳+淬火+回火三道热处理才能满足齿面硬度与芯部韧性的匹配要求；而非调质钢通过钒/钛微合金化与控轧控冷工艺，在终轧后直接获得组织均匀的贝氏体+铁素体复相组织，出厂状态即满足齿轮常用强度级别（如σb≥800MPa、表面硬度HRC28～35），无需任何后续热处理。</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>当前主流适配方案有三类：一是采用VN-Ti复合微合金化非调质钢（如F40MnV），控冷终轧后空冷即可，设备兼容现有热轧线，但需校核齿根弯曲疲劳寿命是否达标；二是选用含硫易切削型非调质钢（如38MnVS6），切削效率提升15%以上，但需评估齿面接触疲劳性能衰减风险；三是改用低碳贝氏体非调质钢（如BHS700），强韧性更优，但对终轧温度与冷却速率控制精度要求更高，产线需加装在线温度闭环监测模块。综合权衡批量稳定性、检测成本与产线改造幅度，第一类VN-Ti系方案在齿轮类中等模数（m=2～6）、中低载荷场景下工程落地性最强。</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>1个异常情况概要：非调质钢齿轮在精加工后出现齿形畸变超差。具体情况：因材料残余应力分布不均，滚齿或剃齿后齿向误差突增0.015mm以上，超出图纸公差带。解决思路：在粗车后增加一次600℃以下低温去应力退火，或改用双面同步铣齿替代单刃滚齿，降低切削力扰动。1个复杂问题概要：同批次非调质钢齿轮在台架耐久试验中发生早期齿面剥落。具体问题：非调质钢表层硬度梯度平缓，导致赫兹接触应力下次表层剪切应力峰值位置上移，加速微裂纹萌生。解决思路：在精加工后增加喷丸强化工序，引入表层压应力场，同时复核原设计齿廓修形量是否需增大0.01～0.02mm以改善载荷分布。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>请简述带传动中，主动轮与从动轮的线速度在理想状态下是否相等，并说明原因。</t>
+          <t>R4-Q039</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>在理想状态下，主动轮与从动轮的线速度是相等的。这是因为带传动依靠摩擦力传递运动，假设带与轮之间无相对滑动、带不可伸长、轮轴平行且安装刚性足够，此时带作为中间柔性件，在任意瞬时与两轮接触点处的线速度必须一致，否则无法实现连续、同步的运动传递。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>实际工程中，为保障线速度一致性，常用三种方案：一是采用高模量聚氨酯同步带配精密齿形轮，靠啮合传动避免打滑，但对装配同轴度和张紧力敏感；二是选用高强度芳纶芯V带配铸铁轮槽，依赖包角与初张力维持摩擦传动，成本低但需定期复紧；三是使用双面齿同步带加浮动张紧轮结构，兼顾传动精度与安装容差。三者中，同步带啮合方案在精度要求高的产线定位机构中最常用，因其能稳定维持线速度匹配，且免维护周期长，适合自动化设备长期运行场景。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1个异常情况概要：带传动运行中突发线速度偏差。具体情况：某输送线主动轮转速恒定，但从动端编码器反馈速度持续偏低2%～3%，且伴随轻微抖动。解决思路：优先排查张紧力衰减和轮槽磨损——用扭矩扳手复核张紧轮预紧力，再用深度规测量轮槽底径磨损量，若超0.15毫米即需更换轮体，避免因接触面下沉导致有效节径变化。1个复杂问题概要：多级带传动系统中线速度累积误差影响末端定位精度。具体问题：三段V带串联驱动机械臂末端执行器，总传动比误差达±0.8%，超出位置重复精度要求。解决思路：改用首级同步带+后两级刚性联轴传动的混合构型，将速度基准前移至高刚度环节，并在首级同步带轮侧加装光电式线速度实时监测点，通过PLC闭环微调电机输出，把误差控制在±0.1%以内。</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>机构与载荷分析</t>
+          <t>制造工艺</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>常见机构的运动传递关系</t>
+          <t>制造成本评估</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>标准化降本</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>简单</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>请简述标准化降本中‘减少零部件种类’这一做法最直接的成本影响。</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>最直接的成本影响是降低采购与仓储环节的固定管理成本，包括供应商协调、物料编码维护、库存盘点频次、安全库存设置和入库检验批次数量。因为每一种零件都需要独立的采购订单处理、入库验收记录、库位占用和周期性呆滞评估，种类减少后，这些事务性工作量呈非线性下降。</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>在机械工程师日常工作中，实现零部件种类精简主要有四种路径：一是通过公差带合并，比如将原本按±0.1和±0.15分别管控的轴类件统一到±0.12公差带，在保证装配间隙和功能前提下减少规格；二是采用模块化接口替代专用连接结构，例如用标准M6内六角圆柱头螺钉+通用垫圈组合替代定制卡扣件；三是借用已有平台件，优先选用本企业已批量验证的轴承、紧固件或铸锻毛坯型号；四是推行断面标准化，对同类支架类零件统一厚度、倒角尺寸和安装孔分布模式。其中，公差带合并和模块化接口最常用，前者实施快但需校核实际装配干涉风险，后者长期效益高但需跨部门对齐接口定义，综合来看，优先采用模块化接口更稳妥，因其不牺牲结构刚度和装配重复性，且便于后期维护备件统一。</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>1个异常情况概要：同类零件合并后出现局部应力集中加剧。具体情况：某机架上原两种不同截面的加强筋板被统一为较厚型材，导致焊接热输入增大、焊缝根部残余应力升高，在振动工况下提前萌生微裂纹。解决思路：在合并前必须复核典型工况下的静刚度与模态响应，结合焊缝区域的几何突变系数做简化应力评估，必要时保留过渡段差异设计。1个复杂问题概要：跨产品线零件通用化引发装配兼容性冲突。具体问题：将A系列电机端盖的定位销孔位置套用于B系列，但B系列壳体铸造收缩率略高，导致销钉过盈配合失效、端盖偏摆超差。解决思路：以铸造材质、壁厚和冷却条件为约束，反向核定各系列毛坯关键尺寸的实测变异带宽，仅在变异交集区间内定义共用特征，而非简单按图纸尺寸对齐。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>在齿轮传动系统中，若主动轮转速恒定，从动轮与主动轮之间通过一个中间惰轮连接，这个惰轮对最终输出转速和转向分别产生什么影响？</t>
+          <t>R4-Q042</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>惰轮不改变最终输出转速大小，只改变从动轮的旋转方向；主动轮与从动轮转向相同，且两者的转速比仅由它们的齿数决定，惰轮的齿数和尺寸不影响传动比。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>工程上实现该惰轮布置，主要有三种常见结构形式：一是单轴双联惰轮，即惰轮与轴固连，结构紧凑但轴向空间受限；二是独立支承惰轮，用两个轴承单独支撑，刚度好、载荷分布均匀，适合中高功率场景；三是悬臂式惰轮，一端固定、一端自由，加工装配简单但易变形，多用于低速轻载。前两种更常用，其中独立支承方案综合刚度、寿命和维护性最优，尤其在需要长期稳定运行的产线设备中被优先选用。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1个异常情况概要：惰轮轴向窜动导致啮合偏载；具体情况是装配时轴承游隙过大或锁紧不到位，运行中惰轮沿轴向微动，造成主动轮与惰轮、惰轮与从动轮两侧啮合深度不一致，引发局部齿面磨损甚至断齿；解决思路是严格控制轴承轴向预紧量，采用双螺母锁紧+力矩校验，并在首台样机试运行后复检轴向位移量。1个复杂问题概要：多级惰轮串接时累积角偏差放大；具体问题是当惰轮不止一个、且分布在不同平面或存在安装基座变形时，各啮合点的相位误差叠加，导致输出端出现周期性转速波动和振动；解决思路是优先采用共面惰轮布局，若必须错位布置，则需在总装阶段实测各级啮合中心距与平行度，用垫片补偿法调整惰轮支座，而非依赖图纸理论值</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>机械设计基础</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>机构与载荷分析</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>常见机构的运动传递关系</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>简单</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>请简述带传动中，主动轮与从动轮的线速度在理想状态下是否相等，并说明原因。</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>在理想状态下，主动轮与从动轮的线速度是相等的。这是因为带传动依靠摩擦力传递运动，假设带与轮之间无相对滑动、带不可伸长、轮轴平行且安装刚性足够，此时带作为中间柔性件，在任意瞬时与两轮接触点处的线速度必须一致，否则无法实现连续、同步的运动传递。</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>实际工程中，为保障线速度一致性，常用三种方案：一是采用高模量聚氨酯同步带配精密齿形轮，靠啮合传动避免打滑，但对装配同轴度和张紧力敏感；二是选用高强度芳纶芯V带配铸铁轮槽，依赖包角与初张力维持摩擦传动，成本低但需定期复紧；三是使用双面齿同步带加浮动张紧轮结构，兼顾传动精度与安装容差。三者中，同步带啮合方案在精度要求高的产线定位机构中最常用，因其能稳定维持线速度匹配，且免维护周期长，适合自动化设备长期运行场景。</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>1个异常情况概要：带传动运行中突发线速度偏差。具体情况：某输送线主动轮转速恒定，但从动端编码器反馈速度持续偏低2%～3%，且伴随轻微抖动。解决思路：优先排查张紧力衰减和轮槽磨损——用扭矩扳手复核张紧轮预紧力，再用深度规测量轮槽底径磨损量，若超0.15毫米即需更换轮体，避免因接触面下沉导致有效节径变化。1个复杂问题概要：多级带传动系统中线速度累积误差影响末端定位精度。具体问题：三段V带串联驱动机械臂末端执行器，总传动比误差达±0.8%，超出位置重复精度要求。解决思路：改用首级同步带+后两级刚性联轴传动的混合构型，将速度基准前移至高刚度环节，并在首级同步带轮侧加装光电式线速度实时监测点，通过PLC闭环微调电机输出，把误差控制在±0.1%以内。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>请简述接触表面粗糙度对磨粒磨损速率的影响规律。</t>
+          <t>R4-Q043</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>在机械零部件实际运行中，当存在硬质颗粒夹杂于摩擦界面时，表面粗糙度直接影响磨粒切入材料表层的深度和频率：粗糙度值越大，峰顶越尖锐、间距越宽，磨粒越容易嵌入并犁削材料；粗糙度值过小，虽减少犁沟深度，但可能因油膜承载能力下降导致边界润滑加剧，反而提升磨粒与表面的直接接触概率。因此，磨粒磨损速率并非随粗糙度单调升高或降低，而是在特定中等粗糙度区间出现最低值。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>当前工程实践中常用三类调控方案：一是通过精车+抛光组合工艺控制Ra0.4～0.8微米，兼顾加工效率与抗磨粒切入能力，但对装配后变形敏感；二是采用喷丸强化后局部研磨，提升表层残余压应力并稳定微观轮廓，适合高载荷齿轮轴类零件，但需同步验证喷丸覆盖率与后续研磨余量匹配性；三是应用微织构表面处理，在关键滑动区刻制5–20微米深储油凹坑，可有效捕获并隔离磨粒，但对批量件一致性要求高、检测成本上升。综合时效性与现场适配性，精车+抛光仍是产线最主流方案，因其工艺链成熟、过程参数易监控、无需新增专用设备。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>异常情况概要：装配后实测磨损速率突增。具体情况：某减速箱输出轴经精车抛光达标（Ra0.6），但装机运行200小时即出现异常振动，拆检发现轴承位磨粒划痕密集。解决思路：核查装配过程是否引入异物（如未清理的键槽铁屑）、轴肩倒角是否过锐导致润滑油膜破裂、以及壳体刚度不足引发轴系微振摆动，放大粗糙峰与磨粒交互作用。复杂问题概要：多工况混合作用下粗糙度最优值漂移。具体问题：同一泵体在低温启动与高温满载交替工况下，原设定Ra0.5表面在冷态磨损快、热态又易发生微动腐蚀。解决思路：改用梯度粗糙度设计——关键密封段保持Ra0.4，承力滑动段过渡至Ra0.7，并通过台架试验标定不同温度区间对应的油膜厚度变化，反向约束表面形貌公差带。</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
         <is>
           <t>机械设计基础</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>失效模式识别</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>磨损与松动失效机理</t>
+          <t>机构与载荷分析</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>简单</t>
+          <t>常见机构的运动传递关系</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>中等</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>在齿轮传动系统中，若主动轮转速恒定，从动轮与主动轮之间通过一个中间惰轮连接，这个惰轮对最终输出转速和转向分别产生什么影响？</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>惰轮不改变最终输出转速大小，只改变从动轮的旋转方向；主动轮与从动轮转向相同，且两者的转速比仅由它们的齿数决定，惰轮的齿数和尺寸不影响传动比。</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>工程上实现该惰轮布置，主要有三种常见结构形式：一是单轴双联惰轮，即惰轮与轴固连，结构紧凑但轴向空间受限；二是独立支承惰轮，用两个轴承单独支撑，刚度好、载荷分布均匀，适合中高功率场景；三是悬臂式惰轮，一端固定、一端自由，加工装配简单但易变形，多用于低速轻载。前两种更常用，其中独立支承方案综合刚度、寿命和维护性最优，尤其在需要长期稳定运行的产线设备中被优先选用。</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>1个异常情况概要：惰轮轴向窜动导致啮合偏载；具体情况是装配时轴承游隙过大或锁紧不到位，运行中惰轮沿轴向微动，造成主动轮与惰轮、惰轮与从动轮两侧啮合深度不一致，引发局部齿面磨损甚至断齿；解决思路是严格控制轴承轴向预紧量，采用双螺母锁紧+力矩校验，并在首台样机试运行后复检轴向位移量。1个复杂问题概要：多级惰轮串接时累积角偏差放大；具体问题是当惰轮不止一个、且分布在不同平面或存在安装基座变形时，各啮合点的相位误差叠加，导致输出端出现周期性转速波动和振动；解决思路是优先采用共面惰轮布局，若必须错位布置，则需在总装阶段实测各级啮合中心距与平行度，用垫片补偿法调整惰轮支座，而非依赖图纸理论值</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>某工业设备外壳由铝合金薄板与不锈钢支架组成，工作环境存在轻微振动。若采用嵌件连接方式固定面板螺钉，嵌件通常应预埋在哪个部件上？请简单说说理由。</t>
+          <t>R4-Q044</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>嵌件应预埋在铝合金薄板上。因为铝合金薄板厚度小、强度低、螺纹保持能力差，直接攻丝易滑牙或脱扣；而不锈钢支架本身刚度高、强度好，且通常厚度足够，可直接加工螺纹或作为支撑基体，无需额外嵌件。</t>
+          <t>校园招聘/社会招聘通用</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>常见方案有四种：一是将嵌件热熔或旋入铝合金薄板，利用铝材塑性实现冷压紧固，装配快、成本低，但需控制嵌入扭矩防止薄板鼓包；二是将嵌件与不锈钢支架焊接后整体装配，虽连接可靠，但焊接易引发表面变形和热影响区腐蚀风险，且不锈钢与嵌件材料匹配要求高，现场返工困难；三是用胶粘+机械铆合双固定嵌件于铝板，提升抗振性，但增加工艺步骤和胶接质量管控点；四是放弃嵌件，在不锈钢支架上直接攻制螺纹并配自攻螺钉穿过铝板，虽简化结构，但铝板无螺纹承力，长期振动下易松动或撕裂。综合装配效率、抗振可靠性、产线适配性和维护便利性，第一种即嵌件预埋于铝合金薄板上为最优方案。</t>
+          <t>制造业</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1个异常情况概要：嵌件在铝板上旋入后局部出现微裂纹。具体情况：铝板厚度≤2.0mm、嵌件外径过大或旋入速度过快时，材料流动不充分，边缘产生拉应力集中裂纹，目视难发现，但振动中会扩展导致连接失效。解决思路：改用低温热胀冷缩辅助旋入工艺，控制旋入转速低于60转/分钟，并在首件后做100%扭力抽检+放大镜外观复检。1个复杂问题概要：设备后期维护需频繁拆装面板螺钉，导致嵌件在铝板内松动。具体问题：铝基体反复受剪切与拉拔载荷，嵌件外螺纹与铝材咬合界面发生微动磨损，预紧力衰减。解决思路：选用带菱形防转齿结构的嵌件，配合铝板背面加设局部加强筋（高度0.8mm以内），并在BOM中明确该嵌件为‘一次性使用’件，维修工单同步提示更换要求。</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>机械设计基础</t>
-        </is>
-      </c>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>连接与紧固设计</t>
+          <t>制造工艺</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>铆接与嵌件连接适用场景</t>
+          <t>制造成本评估</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>材料成本影响</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>制造业</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>机械工程师</t>
+          <t>某企业为降本将某冲压支架的材料从SPCC冷轧钢替换为DC04，两者标称屈服强度相近，但DC04批次间r值离散度达±0.2。请说明该塑性参数波动会如何传导至材料利用率、废品率及边角料价值三个环节，并指出在启动批量切换前，成本评估必须补充验证的两个关键工艺实测数据。</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>校园招聘/社会招聘通用</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>r值反映材料在拉伸时宽向与厚向应变的比值，直接影响板料在冲压成形中抵抗变薄和起皱的能力。r值波动±0.2意味着同一批次材料各卷之间塑性各向异性差异显著：r值偏低时材料更易局部变薄甚至开裂，r值偏高时则更易起皱或侧向流动失控。这种波动会直接导致同一套模具在不同材料批次上表现出不一致的成形稳定性，进而影响材料裁剪布局、成形合格状态和余料形态。</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>针对该场景，常用验证方案有三类：一是仅做单点r值送检，优点是快但无法反映整卷波动，易漏判风险；二是按标准取3个位置（头、中、尾）测r值并记录极差，能识别批次内趋势，但未关联实际成形结果；三是结合模具做小批量试冲，同步采集首件合格率、修边余量偏差和边角料厚度分布，时效略长但数据可直接用于成本建模。最优方案是第三种，因为它把r值波动与真实产线节拍、模具磨损、调机频次等工程变量绑定，确保成本评估不脱离制造现场实际。</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>1个异常情况概要：冲压首件合格，但连续生产50件后废品率陡升。具体情况：因DC04某卷r值偏低且表面粗糙度偏高，导致拉延过程中摩擦状态突变，板料局部减薄加速，模具未及时补偿。解决思路：在换卷交接点增设首中末件厚度扫描和目视褶皱复检，将材料批次号与当班废品记录绑定追溯。1个复杂问题概要：边角料称重价值上升但整体材料成本未降。具体问题：r值偏高批次成形时侧向流动加剧，修边余量增大且切边毛刺增多，导致边角料含油量和铁屑比例升高，回收商拒收或折价。解决思路：在试冲阶段同步测量修边件轮廓偏差和断面毛刺高度，将边角料交付品质指标纳入材料切换准入条件。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>R4-Q047</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>机械设计基础</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>失效模式识别</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>磨损与松动失效机理</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>请简述接触表面粗糙度对磨粒磨损速率的影响规律。</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>在机械零部件实际运行中，当存在硬质颗粒夹杂于摩擦界面时，表面粗糙度直接影响磨粒切入材料表层的深度和频率：粗糙度值越大，峰顶越尖锐、间距越宽，磨粒越容易嵌入并犁削材料；粗糙度值过小，虽减少犁沟深度，但可能因油膜承载能力下降导致边界润滑加剧，反而提升磨粒与表面的直接接触概率。因此，磨粒磨损速率并非随粗糙度单调升高或降低，而是在特定中等粗糙度区间出现最低值。</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>当前工程实践中常用三类调控方案：一是通过精车+抛光组合工艺控制Ra0.4～0.8微米，兼顾加工效率与抗磨粒切入能力，但对装配后变形敏感；二是采用喷丸强化后局部研磨，提升表层残余压应力并稳定微观轮廓，适合高载荷齿轮轴类零件，但需同步验证喷丸覆盖率与后续研磨余量匹配性；三是应用微织构表面处理，在关键滑动区刻制5–20微米深储油凹坑，可有效捕获并隔离磨粒，但对批量件一致性要求高、检测成本上升。综合时效性与现场适配性，精车+抛光仍是产线最主流方案，因其工艺链成熟、过程参数易监控、无需新增专用设备。</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>异常情况概要：装配后实测磨损速率突增。具体情况：某减速箱输出轴经精车抛光达标（Ra0.6），但装机运行200小时即出现异常振动，拆检发现轴承位磨粒划痕密集。解决思路：核查装配过程是否引入异物（如未清理的键槽铁屑）、轴肩倒角是否过锐导致润滑油膜破裂、以及壳体刚度不足引发轴系微振摆动，放大粗糙峰与磨粒交互作用。复杂问题概要：多工况混合作用下粗糙度最优值漂移。具体问题：同一泵体在低温启动与高温满载交替工况下，原设定Ra0.5表面在冷态磨损快、热态又易发生微动腐蚀。解决思路：改用梯度粗糙度设计——关键密封段保持Ra0.4，承力滑动段过渡至Ra0.7，并通过台架试验标定不同温度区间对应的油膜厚度变化，反向约束表面形貌公差带。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R4-Q048</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>机械设计基础</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>连接与紧固设计</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>铆接与嵌件连接适用场景</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>某工业设备外壳由铝合金薄板与不锈钢支架组成，工作环境存在轻微振动。若采用嵌件连接方式固定面板螺钉，嵌件通常应预埋在哪个部件上？请简单说说理由。</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>嵌件应预埋在铝合金薄板上。因为铝合金薄板厚度小、强度低、螺纹保持能力差，直接攻丝易滑牙或脱扣；而不锈钢支架本身刚度高、强度好，且通常厚度足够，可直接加工螺纹或作为支撑基体，无需额外嵌件。</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>常见方案有四种：一是将嵌件热熔或旋入铝合金薄板，利用铝材塑性实现冷压紧固，装配快、成本低，但需控制嵌入扭矩防止薄板鼓包；二是将嵌件与不锈钢支架焊接后整体装配，虽连接可靠，但焊接易引发表面变形和热影响区腐蚀风险，且不锈钢与嵌件材料匹配要求高，现场返工困难；三是用胶粘+机械铆合双固定嵌件于铝板，提升抗振性，但增加工艺步骤和胶接质量管控点；四是放弃嵌件，在不锈钢支架上直接攻制螺纹并配自攻螺钉穿过铝板，虽简化结构，但铝板无螺纹承力，长期振动下易松动或撕裂。综合装配效率、抗振可靠性、产线适配性和维护便利性，第一种即嵌件预埋于铝合金薄板上为最优方案。</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：嵌件在铝板上旋入后局部出现微裂纹。具体情况：铝板厚度≤2.0mm、嵌件外径过大或旋入速度过快时，材料流动不充分，边缘产生拉应力集中裂纹，目视难发现，但振动中会扩展导致连接失效。解决思路：改用低温热胀冷缩辅助旋入工艺，控制旋入转速低于60转/分钟，并在首件后做100%扭力抽检+放大镜外观复检。1个复杂问题概要：设备后期维护需频繁拆装面板螺钉，导致嵌件在铝板内松动。具体问题：铝基体反复受剪切与拉拔载荷，嵌件外螺纹与铝材咬合界面发生微动磨损，预紧力衰减。解决思路：选用带菱形防转齿结构的嵌件，配合铝板背面加设局部加强筋（高度0.8mm以内），并在BOM中明确该嵌件为‘一次性使用’件，维修工单同步提示更换要求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>R4-Q049</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>工程图与公差</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>工程图表达</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>技术要求与图面信息一致性</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>某张装配图的明细栏中列出一个零件材料为‘Q235B’，但该零件的单件图上技术要求却写‘调质处理，硬度220–250HBW’。这两处信息存在明显矛盾，作为设计校核人员，你第一步会怎么做？请简述判断逻辑。</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>第一步是核查Q235B材料是否具备实施调质处理的工艺可行性——因为Q235B是低碳普通碳素结构钢，碳含量约0.17%～0.22%，淬透性极低，无法通过常规调质工艺获得220–250HBW的稳定硬度，该技术要求与材料本体特性存在根本性冲突。</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>常见校核路径有四种：一是查GB/T 700—2019确认Q235B成分与力学性能边界，明确其不适用于调质；二是对照JB/T 6045—2021《机械零件热处理工艺选择导则》，确认调质适用材料需为中碳钢（如45钢）或合金结构钢；三是调阅企业《常用材料热处理适配清单》，核实Q235B仅允许正火、退火或不热处理；四是追溯设计输入依据，确认是否误标材料牌号或误选热处理类型。其中，优先采用第一种方法，因其直接、权威、无需依赖内部文档，且能在5分钟内完成标准条款核对，时效性与可靠性兼顾。</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>1个异常情况概要：明细栏与单件图材料/热处理信息不一致但已进入试制阶段。具体情况：图纸已下发车间，操作工按单件图执行调质，但Q235B零件在淬火时开裂或硬度不达标，导致批量报废。解决思路：立即暂停该零件加工，组织设计、工艺、质量三方联合评审，以材料可焊性、冷热加工变形、后续装配刚度为约束，同步评估更换材料（如改用45钢）或取消调质改为表面淬火+回火的可行性，并更新全部关联图样版本。1个复杂问题概要：同一零件在不同图纸层级出现多源信息冲突且无主次标识。具体问题：装配图、单件图、BOM表三处材料及热处理要求互不统一，且无‘以某图为准’说明。解决思路：依据GB/T 4457.2—2018《技术制图 图样管理规则》，以单件图的技术要求为最终执行依据，但须同步启动设计变更流程，统一所有源头文件，并在ERP系统中标记生效版本与替换关系，确保制造、检验、采购执行口径唯一。</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>R4-Q052</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>校园招聘/社会招聘通用</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>制造业</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>机械工程师</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
         <is>
           <t>工程图与公差</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>工程图表达</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>技术要求与图面信息一致性</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>中等</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>制造业</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>机械工程师</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>校园招聘/社会招聘通用</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>设计变更表达</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>变更前后验证要求</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>某传动支架图纸中，原设计将两处安装孔的基准体系设定为‘一面两销’，现因轻量化需求将其中一销孔改为槽形结构。请简述你如何界定该变更对现有检测工装、产线SPC控制点及最终装配功能的影响，并说明必须开展的变更后验证类型。</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>这个变更本质是基准体系从‘一面两销’降级为‘一面一销一槽’，导致定位自由度减少、重复定位精度下降、基准传递路径改变。需据此评估检测工装是否仍能复现原定位状态，SPC控制点是否仍能稳定采集关键尺寸特征，以及装配时螺栓预紧力分布和支架姿态是否发生偏移。</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>常见应对方案有三种：一是改造现有工装，在槽口位置增加可浮动定位销或弹性压紧块，兼顾槽宽公差与定位刚性，实施快、成本低但对槽宽一致性依赖高；二是重新设计专用工装，采用面-销-槽三点约束并引入槽中心找正机构，定位稳定性好但开发周期长；三是维持原工装但收紧槽宽公差带并增加首件三坐标比对，短期可行但放大制造风险。综合权衡时效性与稳健性，优先选用第一种方案，同步补充槽宽过程能力分析和首件装配干涉检查。</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1个异常情况概要：槽口加工后实际轮廓呈喇叭状或单侧偏磨。具体情况：铣削参数不当或夹具让位不足导致槽口两端深度不一致，造成定位销插入时倾斜，引发工装虚压和检测数据漂移。解决思路：在首件检验中增加槽口两端深度差测量项，并要求机加班组反馈刀具磨损趋势。1个复杂问题概要：装配状态下支架因槽口间隙累积导致传动轴系同轴度超差。具体问题：槽宽公差叠加销轴公差与安装面平面度误差，使支架在螺栓预紧过程中产生微转动，影响后续齿轮啮合间隙。解决思路：开展装配状态下的刚体运动仿真，结合实测槽口-销轴配合间隙分布，重新分配关键尺寸公差链，并在SPC中将‘装配后轴向偏移量’设为新增控制点。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
